--- a/results/Int Task Remove ACC 0.6/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.6/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.0033794162826420336 +/- 0.0024790001918914943</t>
+          <t>0.00046082949308758894 +/- 0.0016741200946514766</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,377 +886,377 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.003072196620583689 +/- 0.0021602686236281625</t>
+          <t>0.005273937532002115 +/- 0.0013748818824472833</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0010240655401946076 +/- 0.0012749513157182476</t>
+          <t>-0.0030721966205836783 +/- 0.0016512560672398318</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.001792114695340552 +/- 0.0012384420504298818</t>
+          <t>0.0023553507424475596 +/- 0.0015395080776623602</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.004608294930875545 +/- 0.0017439207748004733</t>
+          <t>-0.0043522785458268935 +/- 0.0010304460725805576</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.0014848950332820743 +/- 0.0018240156815726555</t>
+          <t>-0.012800819252432104 +/- 0.002035290006590036</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>-0.0003072196620583556 +/- 0.0003396441157557835</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-0.01582181259600609 +/- 0.001474263189850282</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.01377368151561702 +/- 0.003982351122447684</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.003840245775729623 +/- 0.002076733209490351</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.002764976958525389 +/- 0.001396639190679564</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-0.001894521249359904 +/- 0.0014125052968902891</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>-0.003430619559651793 +/- 0.0015369514613214218</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.013773681515617054 +/- 0.001705153692303831</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-0.0022529441884280186 +/- 0.001556444869797317</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>-0.022939068100358385 +/- 0.0013312852022529427</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.0008192524321557037 +/- 0.0012993935013261273</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.0013312852022529964 +/- 0.0011942553804086505</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>-0.010803891449052704 +/- 0.0016583855341220249</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>-0.0023041474654377446 +/- 0.0015740323757234393</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0047619047619048005 +/- 0.0013748818824472649</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>-0.0008192524321556149 +/- 0.001589777234640042</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.004045058883768604 +/- 0.0008079740828499718</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.00440348182283673 +/- 0.0012583928036297507</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-0.0013312852022528744 +/- 0.0003396441157557835</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.010496671786994394 +/- 0.0021993580742359973</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.003891449052739415 +/- 0.001731851973915788</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.005376344086021567 +/- 0.0015906015941637589</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-0.005171530977982541 +/- 0.0015437596960246995</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.0004096262160778852 +/- 0.0005971276902043424</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>-0.000563236047106963 +/- 0.0007402371886738778</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.0019457245263697297 +/- 0.001583166905656971</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-0.0054275473630312045 +/- 0.001654428512176509</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>-0.00035842293906808155 +/- 0.0003278609440569643</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.003123399897593493 +/- 0.00048305074920924684</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.001792114695340552 +/- 0.001195352537627133</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0011776753712238075 +/- 0.0013361995238812077</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-0.0005632360471069852 +/- 0.00042532636266859385</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.009216589861751168 +/- 0.0013154360039595628</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.0005120327700972483 +/- 0.0011898566347795536</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>-0.005273937532002016 +/- 0.001190957844302404</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-0.017357910906297968 +/- 0.0017655852175695707</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.010035842293906827 +/- 0.0017469249471819823</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.0004096262160778741 +/- 0.0012073554656991106</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>-0.011213517665130523 +/- 0.0009835828321709443</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>4.4408920985006264e-17 +/- 0.0007932377565196976</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>-0.011008704557091598 +/- 0.0010801343118140684</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>-0.0034818228366615077 +/- 0.0010934027907866248</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-0.0012800819252431817 +/- 0.0011276352045849983</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-0.0008704557091653631 +/- 0.001355678678430496</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-0.0012800819252431705 +/- 0.0008644108047175569</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>-0.0009728622631847928 +/- 0.0002757380853627353</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>-0.010189452124935949 +/- 0.0007748461828172902</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.0072196620583717674 +/- 0.0014919408381293708</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-0.00788530465949816 +/- 0.0015731993339208618</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.0019457245263697297 +/- 0.0007168458781362074</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>-0.008550947260624631 +/- 0.000858323328942151</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>-0.01920122887864819 +/- 0.0020385078584121232</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.0004608294930876111 +/- 0.0003584229390681243</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-0.0028673835125447634 +/- 0.0009216589861751099</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-0.00563236047107013 +/- 0.0015698627462115617</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>0.004454685099846445 +/- 0.002244199385643731</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-0.004301075268817167 +/- 0.0012160104543817425</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
           <t>-0.00010240655401945186 +/- 0.00020481310803890373</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-0.005683563748079867 +/- 0.0015094114667673914</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.015873015873015893 +/- 0.001969829396996545</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.0013824884792627112 +/- 0.003649827626665978</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.00209933435739893 +/- 0.0015437596960247199</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.0019457245263697297 +/- 0.0017257859238456346</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0.0016385048643113632 +/- 0.001899358626829629</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0.01597542242703538 +/- 0.002229548495348402</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.0036354326676907634 +/- 0.002704095427856836</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>-0.004813108038914449 +/- 0.002063434887824887</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0.005785970302099352 +/- 0.001553916119354164</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>-0.00588837685611876 +/- 0.0017020757950429852</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>-0.007936507936507898 +/- 0.00147070216245214</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-0.00040962621607780746 +/- 0.00020481310803890376</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.0035330261136713114 +/- 0.0011551985839916303</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.009728622631848472 +/- 0.0012749513157182565</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.004352278545826971 +/- 0.0013004019558832665</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.0013824884792627222 +/- 0.0010506034064865952</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>0.004864311315924241 +/- 0.001877841353906001</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>0.00025601638504867407 +/- 0.00034348202419354765</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0.007629288274449586 +/- 0.002066608916601191</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.002508960573476737 +/- 0.0017803726216808467</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.004557091653865886 +/- 0.0013633924173778271</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.0024065540194571967 +/- 0.001683490242987574</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>-0.0008192524321556149 +/- 0.0004692857854537224</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.0008704557091654297 +/- 0.0013164321691943206</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.001740911418330815 +/- 0.0019457245263696911</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.016589861751152114 +/- 0.0020506896461342287</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>-0.0026113671274961116 +/- 0.000665642601126473</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>-0.0007168458781361631 +/- 0.0005701755619897317</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.007936507936507964 +/- 0.0013204093147186635</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0006144393241167889 +/- 0.0014980787340837507</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.0008704557091654408 +/- 0.0006080052271908748</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.0024065540194572743 +/- 0.0012963634307395998</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.0006144393241167667 +/- 0.0010189323472674006</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0020993343573989186 +/- 0.0018945212493599423</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-0.0010752688172042779 +/- 0.0025952536400356877</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.0011264720942140815 +/- 0.0012708319145919933</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-0.002201740911418293 +/- 0.001996927803379408</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>-0.0043522785458268935 +/- 0.0008014580564515344</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>-0.0007168458781361631 +/- 0.0005221730172649787</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>-0.0011776753712237076 +/- 0.001255263765707252</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>-0.010291858678955424 +/- 0.001852539940105034</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.0004096262160778741 +/- 0.002299021435805812</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.01582181259600618 +/- 0.00277113346190165</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.0005120327700973259 +/- 0.0007241236878510562</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.0003072196620584111 +/- 0.000799820755341191</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.0032258064516129336 +/- 0.0008883436545262294</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.0021505376344086334 +/- 0.0016159481656998949</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-0.016026625704045006 +/- 0.0023018706393229944</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.0003072196620584222 +/- 0.0004096262160778546</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.00035842293906813706 +/- 0.0019165353069342435</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>-0.022683051715309755 +/- 0.002786229976531031</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.001536098310291889 +/- 0.0006869640483870375</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-0.0017409114183307372 +/- 0.0021260153089632944</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-0.0008704557091653408 +/- 0.0016037337187266528</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-0.005888376856118771 +/- 0.002447602335425935</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-0.005273937532002004 +/- 0.0006080052271908748</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>-5.120327700972593e-05 +/- 0.00015360983102917782</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.0006144393241167889 +/- 0.0013701063144147202</t>
+          <t>-0.0034306195596517817 +/- 0.0009728622631848564</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0007168458781361409 +/- 0.0013391394603811688</t>
+          <t>-0.00706605222734249 +/- 0.00099286837837506</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.0002560163850486852 +/- 0.0008942267893790577</t>
+          <t>-0.0003584229390680593 +/- 0.0008583233289421682</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.0022017409114183815 +/- 0.0012759790880058507</t>
+          <t>-0.007424475166410616 +/- 0.0011041402280003788</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.008909370199692745 +/- 0.0012790574497487815</t>
+          <t>0.0026625704045059374 +/- 0.001140351123979506</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.008704557091653842 +/- 0.0008868667729487387</t>
+          <t>-0.006554019457245231 +/- 0.0008506527253372185</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>5.120327700973704e-05 +/- 0.0001536098310292111</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-5.120327700968153e-05 +/- 0.0007402371886738869</t>
+          <t>0.0013312852022529964 +/- 0.0006945550417946855</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.002304147465437845 +/- 0.0007680491551459334</t>
+          <t>0.00020481310803895924 +/- 0.0006144393241167575</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,52 +1266,52 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.0005632360471070852 +/- 0.000275738085362758</t>
+          <t>0.0012288786482335333 +/- 0.0003396441157557835</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.003174603174603152 +/- 0.0014804743773477885</t>
+          <t>-0.008602150537634367 +/- 0.000551476170725516</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>5.120327700973704e-05 +/- 0.0001536098310292111</t>
+          <t>-0.0025089605734766817 +/- 0.0001536098310291778</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0010752688172043444 +/- 0.0006250156485270576</t>
+          <t>0.0019457245263697297 +/- 0.001207355465699089</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-0.0027137736815155745 +/- 0.0009728622631848471</t>
+          <t>-0.007014848950332775 +/- 0.0006496967506630473</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>-0.005273937532002016 +/- 0.0013938205416094314</t>
+          <t>0.0009728622631848816 +/- 0.0011997311330117725</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0011264720942139705 +/- 0.00030721966205835564</t>
+          <t>-0.0004608294930875223 +/- 0.0007748461828172645</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>-0.007782898105478708 +/- 0.0012073554656990878</t>
+          <t>-0.007117255504352238 +/- 0.0005815574342857118</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-0.008038914490527372 +/- 0.0010506034064865868</t>
+          <t>-0.005632360471070097 +/- 0.0009981356215882297</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0012288786482335223 +/- 0.0010543400041973328</t>
+          <t>0.0024577572964670225 +/- 0.0010691558124844268</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.010465724751438976 +/- 0.0017355441079829398</t>
+          <t>0.006384092098377836 +/- 0.0019411027724742225</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.006593406593406537 +/- 0.0011271930522521107</t>
+          <t>0.003401360544217713 +/- 0.0016915991496854624</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.002250130821559437 +/- 0.0017675924389382082</t>
+          <t>0.0029304029304029755 +/- 0.0018456506633750343</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0010989010989010395 +/- 0.0012699802301948209</t>
+          <t>0.001255886970172726 +/- 0.0012860497883249152</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0034536891679748383 +/- 0.0015906524493532932</t>
+          <t>0.00047095761381477086 +/- 0.001157160878466554</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.0014128728414443126 +/- 0.0014435493693494318</t>
+          <t>-0.0008372579801150914 +/- 0.00155584183645406</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0005232862375719183 +/- 0.00023402071978018273</t>
+          <t>5.232862375720293e-05 +/- 0.0001569858712716088</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0046049188906331475 +/- 0.0021294599633046307</t>
+          <t>-0.0015698587127158214 +/- 0.001384485249118056</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.004604918890633136 +/- 0.004985245573548738</t>
+          <t>0.01930926216640506 +/- 0.0047237996739236034</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.005913134484563131 +/- 0.0026377986731823365</t>
+          <t>0.03369963369963373 +/- 0.005685306899232271</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.006802721088435315 +/- 0.0014041243186811915</t>
+          <t>0.003035060177917348 +/- 0.0019126809924120383</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.004814233385661915 +/- 0.0013402667163648007</t>
+          <t>0.0058608058608058955 +/- 0.0014387992762812552</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.004918890633176298 +/- 0.0017386967792607135</t>
+          <t>-5.232862375715852e-05 +/- 0.0026728608663782647</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.008424908424908362 +/- 0.0029364705068755936</t>
+          <t>0.00983778126635273 +/- 0.002727119669449591</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.0385138670852956 +/- 0.0037821687073977383</t>
+          <t>0.022135007849293585 +/- 0.003957995415458024</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.002145473574045054 +/- 0.002237928286796758</t>
+          <t>0.005389848246991136 +/- 0.0016221873364730425</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-0.0006279434850863907 +/- 0.000959199517520841</t>
+          <t>0.00308738880167454 +/- 0.001488379136925994</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>-0.008215593929879694 +/- 0.0022815519996432806</t>
+          <t>0.006436420722135028 +/- 0.001481001747575609</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.01465201465201459 +/- 0.0019994739062839284</t>
+          <t>0.005075876504447974 +/- 0.001282851980338174</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00047095761381472646 +/- 0.00015698587127157548</t>
+          <t>0.0006279434850864129 +/- 0.00020931449502876732</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0011512297226582314 +/- 0.0013805239098139976</t>
+          <t>0.008843537414966008 +/- 0.0016456499417599583</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.0036630036630036166 +/- 0.0016547763789473491</t>
+          <t>-0.013814756671899497 +/- 0.0021978021978021948</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.00209314495028774 +/- 0.0014234924655924007</t>
+          <t>0.0001569858712716199 +/- 0.0012828519803381598</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.00010465724751442806 +/- 0.0006942176431931754</t>
+          <t>-0.0002616431187859369 +/- 0.0007492318714430466</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.0004186289900576012 +/- 0.0012338907506595142</t>
+          <t>0.0011512297226582869 +/- 0.001732385699345551</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.000889586603872361 +/- 0.0004086996167402729</t>
+          <t>0.0008372579801151803 +/- 0.000256356854294403</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.011198325484039717 +/- 0.0018896358017025286</t>
+          <t>-0.003924646781789609 +/- 0.002534024073846818</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.010727367870225069 +/- 0.002283951108612796</t>
+          <t>-0.014076399790685468 +/- 0.002333762754681078</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.0023024594453165403 +/- 0.0018157353817789055</t>
+          <t>-0.010099424385138634 +/- 0.0028474658001910683</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0168498168498169 +/- 0.003085170690315779</t>
+          <t>-0.018995290423861843 +/- 0.002499205428835077</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.0001569858712716199 +/- 0.0006213679794368401</t>
+          <t>0.00020931449502881172 +/- 0.0002563568542944574</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0007849293563579884 +/- 0.00026164311878595914</t>
+          <t>-0.00041862899005753464 +/- 0.00031397174254315096</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.0037676609105181226 +/- 0.0017637152848092785</t>
+          <t>-0.000994243851386667 +/- 0.002568370736118886</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.005023547880690782 +/- 0.0031501657652103733</t>
+          <t>-0.012925170068027191 +/- 0.002269518413626527</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.0006802721088434826 +/- 0.0006213679794368166</t>
+          <t>0.0005232862375720182 +/- 0.0002340207197802076</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-0.001255886970172726 +/- 0.0007098199877682207</t>
+          <t>0.00020931449502881172 +/- 0.0007098199877682109</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.0019361590790161753 +/- 0.001605218383064143</t>
+          <t>0.00010465724751445027 +/- 0.0006535843012452633</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.004133961276818354 +/- 0.0027535996058446676</t>
+          <t>-0.0049188906331763095 +/- 0.0018750887354441665</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.002093144950287873 +/- 0.0010200726682165465</t>
+          <t>0.0012558869701727148 +/- 0.000479599758760392</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.000889586603872261 +/- 0.000877187577929874</t>
+          <t>-0.0015175300889586295 +/- 0.001083846948048574</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.003976975405546779 +/- 0.001988487702773407</t>
+          <t>-0.002511773940345352 +/- 0.001566366252966599</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.000575614861329099 +/- 0.0010582809218292173</t>
+          <t>0.003087388801674551 +/- 0.0007565061378755142</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0093144950287807 +/- 0.0007690705628832695</t>
+          <t>0.006331763474620633 +/- 0.00201923405353999</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>-0.0021454735740450647 +/- 0.0016120273993458273</t>
+          <t>-0.007378335949764503 +/- 0.002403131868802724</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>-0.013082155939298856 +/- 0.002093144950287798</t>
+          <t>-0.003244374672946071 +/- 0.001340266716364799</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.013291470434327634 +/- 0.0019040717319372263</t>
+          <t>-0.011669283097854487 +/- 0.002158198914421912</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.0003139717425432287 +/- 0.0006279434850863464</t>
+          <t>0.0006802721088435826 +/- 0.0007418862835561279</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.009262166405023609 +/- 0.0019162567685610304</t>
+          <t>-0.005913134484563032 +/- 0.0012828519803381852</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.004447933019361638 +/- 0.002343130630794154</t>
+          <t>0.0035060177917320854 +/- 0.0018134718420893172</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.001674515960230194 +/- 0.001912680992412029</t>
+          <t>0.0025641025641025884 +/- 0.002124954526870432</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.015593929879644119 +/- 0.0019269442846176813</t>
+          <t>0.004918890633176365 +/- 0.001845650663375039</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.0007326007326006855 +/- 0.0005827068930224662</t>
+          <t>-0.0008895866038722833 +/- 0.0005756148613291465</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.00010465724751436145 +/- 0.0004561903656243523</t>
+          <t>-0.00010465724751435035 +/- 0.0005127137085888468</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00026164311878601465 +/- 0.0004218868523442676</t>
+          <t>-0.00015698587127155328 +/- 0.0006213679794368288</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.0006802721088435826 +/- 0.0030695990321428527</t>
+          <t>-0.01585557299843011 +/- 0.001462395459181809</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.00910518053375201 +/- 0.0013484143094427224</t>
+          <t>-0.006750392464678146 +/- 0.0016622061930160641</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0004709576138147931 +/- 0.0011332500171484909</t>
+          <t>-0.0016221873364730354 +/- 0.0012699802301948406</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-0.01219256933542654 +/- 0.0022574206813315476</t>
+          <t>-0.009157509157509115 +/- 0.001265660557032743</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>5.232862375713632e-05 +/- 0.0017268445839874497</t>
+          <t>0.001098901098901106 +/- 0.0017737782581557558</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0003663003663004205 +/- 0.0005756148613291515</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.017634746206174834 +/- 0.002132672304794854</t>
+          <t>-0.015175300889586574 +/- 0.0010976544721822393</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.004081632653061262 +/- 0.0022785495611802424</t>
+          <t>0.006017791732077471 +/- 0.0028589823923909382</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.000941915227629575 +/- 0.0022543861045042457</t>
+          <t>-0.005128205128205099 +/- 0.0016179617827043664</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.0004186289900575013 +/- 0.0008038875717287794</t>
+          <t>-0.0008895866038722722 +/- 0.0012171327419793925</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1661,62 +1661,62 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.0018838304552589724 +/- 0.0011747746897249332</t>
+          <t>-0.004657247514390362 +/- 0.0012699802301948332</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.001622187336473091 +/- 0.0017268445839874469</t>
+          <t>-0.0027210884353741417 +/- 0.0005127137085888514</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.0010465724751439586 +/- 0.0012817842714720879</t>
+          <t>-0.001046572475143892 +/- 0.0007020621593405979</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.00041862899005759016 +/- 0.0015663662529666006</t>
+          <t>-0.005965463108320223 +/- 0.001286049788324918</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.0010989010989010395 +/- 0.0013933570858915968</t>
+          <t>-0.002616431187859736 +/- 0.0005732313527003347</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-5.232862375724734e-05 +/- 0.0016456499417599377</t>
+          <t>-0.005232862375719483 +/- 0.0013029722237560125</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>-0.00026164311878600354 +/- 0.0003510310796703238</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0009942438513867557 +/- 0.0008582532426403436</t>
+          <t>5.2328623757225136e-05 +/- 0.0004936672491918802</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0003663003663003317 +/- 0.00047095761381474744</t>
+          <t>-0.00010465724751436145 +/- 0.0005635965261260589</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>-0.0003663003663004205 +/- 0.00023979987938024688</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>-0.0004186289900576012 +/- 0.0006102513757033574</t>
+          <t>-0.0012035583464154564 +/- 0.00047095761381477335</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>-0.0013605442176871207 +/- 0.0010517923203684954</t>
+          <t>-0.002354788069073732 +/- 0.0014282934656154919</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0015175300889585964 +/- 0.0007565061378755003</t>
+          <t>-0.001046572475143881 +/- 0.0004680414395604151</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0009942438513866447 +/- 0.0015949503562666914</t>
+          <t>0.0020408163265306146 +/- 0.0010838469480485505</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>5.232862375714742e-05 +/- 0.0014511171767516457</t>
+          <t>-0.009052851909994752 +/- 0.0016221873364730495</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.0007326007326007855 +/- 0.0003471088215965893</t>
+          <t>-0.0005232862375719072 +/- 0.0007761589206798208</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.000209314495028734 +/- 0.0009983665111637095</t>
+          <t>-0.0004186289900575124 +/- 0.0010926537424291599</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.003819989534275192 +/- 0.0013248549347118935</t>
+          <t>-0.005808477237048626 +/- 0.0012260988502208125</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.0010989010989010395 +/- 0.0007193996381406439</t>
+          <t>-0.0018838304552589945 +/- 0.001483772567112302</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.022351080653663737 +/- 0.0030208853520072494</t>
+          <t>-0.020295202952029488 +/- 0.00118461808404026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.049762783342119185 +/- 0.002044356292004786</t>
+          <t>-0.011913547706905636 +/- 0.0013377519810700543</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.03769109119662628 +/- 0.0011367347734764302</t>
+          <t>-0.02013705851344224 +/- 0.0009946210998477906</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.011860832894043206 +/- 0.0010608651448338515</t>
+          <t>-0.001265155508697935 +/- 0.0010057345296963034</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.04438587243015289 +/- 0.0017923036373220995</t>
+          <t>-0.018133895624670528 +/- 0.0014378683918804102</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0038481813389562246 +/- 0.0018570284611289893</t>
+          <t>0.005007907221929386 +/- 0.0012078481009372255</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0008434370057986418 +/- 0.0004831392403748964</t>
+          <t>0.00036900369003693977 +/- 0.00024156962018747125</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.0030574591460200582 +/- 0.0009946210998478448</t>
+          <t>0.00021085925144967988 +/- 0.001358365706560353</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.023089088033737437 +/- 0.002366889227268723</t>
+          <t>0.026199261992619925 +/- 0.0026987719000886178</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.013231418028465957 +/- 0.0038046073960497696</t>
+          <t>0.04206642066420668 +/- 0.0030538214776932616</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.002635740643120743 +/- 0.0017162699626884306</t>
+          <t>0.0004744333157617575 +/- 0.0012124406958355328</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>-0.03832366895097524 +/- 0.0019589777729111277</t>
+          <t>-0.017659462308908812 +/- 0.0010071150856374638</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.04802319451765952 +/- 0.0011893003872091347</t>
+          <t>-0.016657880864522946 +/- 0.0011597258829731253</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-0.01739588824459678 +/- 0.004473000197279141</t>
+          <t>-0.019082762256193965 +/- 0.003307198132073383</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.007801792303637334 +/- 0.0032734158558271054</t>
+          <t>0.0016868740115972946 +/- 0.0020524957653064715</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.0015287295730099903 +/- 0.0015359833720962922</t>
+          <t>-0.0013705851344227415 +/- 0.001358365706560386</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.02329994728518716 +/- 0.0023668892272686822</t>
+          <t>-0.013336847654190843 +/- 0.0010015814443858808</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.0024248813916710856 +/- 0.0016703194009230129</t>
+          <t>-0.005535055350553475 +/- 0.0014193897752067697</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.018924617817606813 +/- 0.002420867159347389</t>
+          <t>-0.014812862414338424 +/- 0.0013837010804856823</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.0008961518186610728 +/- 0.0007473614590805498</t>
+          <t>0.0003690036900369176 +/- 0.0005297773126579447</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.011597258829731205 +/- 0.0024612793948189117</t>
+          <t>-0.003426462836056898 +/- 0.002407053253944311</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.001792303637322079 +/- 0.0023715807863367378</t>
+          <t>-0.005956773853452812 +/- 0.0014731880455964399</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.003110173958882434 +/- 0.0013220807805993265</t>
+          <t>0.0022667369530838368 +/- 0.0015468002900496745</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.000790722192936244 +/- 0.0008581349813442186</t>
+          <t>-0.0010015814443858461 +/- 0.001300892217106283</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0026357406431206875 +/- 0.0008820875345641162</t>
+          <t>0.002055877701634201 +/- 0.0007977198708709308</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.0003690036900368621 +/- 0.00024156962018742037</t>
+          <t>-0.0009488666315234263 +/- 0.0005164975735968686</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.001739588824459648 +/- 0.0013346324619053598</t>
+          <t>0.0009488666315234818 +/- 0.0016636514325840137</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.004111755403268358 +/- 0.0019267967192933197</t>
+          <t>-0.00511333684765416 +/- 0.0018115804193399579</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-0.005218766473379055 +/- 0.001978737414773166</t>
+          <t>-0.00448075909330522 +/- 0.0015141177244433442</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0031101739588824786 +/- 0.0017712490897639815</t>
+          <t>-0.014127569847127052 +/- 0.001696729250335382</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.000474433315761702 +/- 0.000369003690036897</t>
+          <t>0.0006852925672114152 +/- 0.0004744333157617328</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.0004217185028993264 +/- 0.0005677559100827231</t>
+          <t>0.0013705851344228193 +/- 0.0003496705103168688</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.0062203479177649346 +/- 0.002246418107818939</t>
+          <t>-0.0023721665788086098 +/- 0.0017992670707302073</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.006483921982076946 +/- 0.002001080958998677</t>
+          <t>0.00031628887717451983 +/- 0.001686874011597276</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.000421718502899282 +/- 0.0003162888771744754</t>
+          <t>0.00010542962572483994 +/- 0.00021085925144967988</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0007380073800737797 +/- 0.0005870073128972173</t>
+          <t>0.0006325777543490063 +/- 0.0004595570841898501</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0003162888771744643 +/- 0.0008883658168873428</t>
+          <t>0.004217185028993176 +/- 0.0014144868597784712</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.0035318924617818047 +/- 0.002973134138577462</t>
+          <t>0.0003162888771745087 +/- 0.002188775908489894</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.00010542962572481773 +/- 0.00021085925144963545</t>
+          <t>0.00047443331576176864 +/- 0.00043788212245218354</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.003531892461781749 +/- 0.0013136463673565836</t>
+          <t>0.002899314707432832 +/- 0.0019188481521561975</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.00026357406431209984 +/- 0.0014388343768008778</t>
+          <t>0.0010015814443858906 +/- 0.0016577949597803127</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.008434370057986274 +/- 0.001509522515896285</t>
+          <t>0.0032683183974697274 +/- 0.0016127631566450597</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.006852925672113852 +/- 0.0028582902924040063</t>
+          <t>0.0005798629414865864 +/- 0.0015359833720963076</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.015234580917237794 +/- 0.003387311297083269</t>
+          <t>-0.010911966262519756 +/- 0.0017961755442699866</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-2.2204460492503132e-17 +/- 0.001527820426588225</t>
+          <t>0.00015814443858728212 +/- 0.002298390021780889</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.009857670005271468 +/- 0.00137564452827623</t>
+          <t>-0.0032683183974696827 +/- 0.001350157983644247</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>1.1102230246251566e-17 +/- 0.0002357478099630778</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.005956773853452802 +/- 0.0022121386671963375</t>
+          <t>0.0023721665788086765 +/- 0.001654439096096512</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>-0.005218766473379055 +/- 0.001921742344075726</t>
+          <t>0.0019504480759093723 +/- 0.001270634769973</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.004691618344754844 +/- 0.0021013317267258615</t>
+          <t>0.008276225619399113 +/- 0.00216130732735898</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.013231418028466047 +/- 0.00294873300388973</t>
+          <t>-0.007749077490774891 +/- 0.0015997881819181207</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.001159725882973095 +/- 0.0003162888771744754</t>
+          <t>-5.2714812862397764e-05 +/- 0.00028387795504134823</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.0012651555086979128 +/- 0.0004831392403748698</t>
+          <t>5.271481286241997e-05 +/- 0.00015814443858725992</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-0.0036373220875066227 +/- 0.0004973105499239036</t>
+          <t>-0.00010542962572480663 +/- 0.0011007176076869199</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.011017395888244652 +/- 0.002074714670970412</t>
+          <t>-0.003584607274644158 +/- 0.0018077415075890564</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.0012651555086979239 +/- 0.0007150585116631719</t>
+          <t>0.0074327886136004604 +/- 0.002034136149876085</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.000527148128624122 +/- 0.0005271481286241553</t>
+          <t>0.00036900369003693977 +/- 0.00041171585007415283</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.003584607274644147 +/- 0.0011974503628466662</t>
+          <t>0.0011070110701107306 +/- 0.0027538129439344163</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.004533473906167618 +/- 0.000675078991822127</t>
+          <t>0.010437532946758088 +/- 0.0012651555086979304</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0013705851344227638 +/- 0.00042171850289930983</t>
+          <t>0.0010542962572483105 +/- 0.00047149561992616807</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.000896151818661084 +/- 0.0014349665354576955</t>
+          <t>0.000158144438587271 +/- 0.002495477148876049</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.004849762783342137 +/- 0.0025148888649186227</t>
+          <t>0.0062203479177649346 +/- 0.0019267967192933076</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.01576172904586195 +/- 0.0019646436640573827</t>
+          <t>-0.004797047970479684 +/- 0.0028137071470917324</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-0.008645229309435986 +/- 0.001513199799094092</t>
+          <t>0.007696362677912539 +/- 0.0013168156032468976</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.00010542962572481773 +/- 0.00021085925144963545</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.007801792303637356 +/- 0.001680271739642523</t>
+          <t>0.006958355297838737 +/- 0.0013294169966176447</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.001476014760147648 +/- 0.0012651555086979406</t>
+          <t>-0.0001581444385872155 +/- 0.0015997881819181427</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.0020031628887717257 +/- 0.0006584078016234626</t>
+          <t>0.00395361096468112 +/- 0.0014956521833538444</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.0019504480759093613 +/- 0.0018867190477778928</t>
+          <t>0.006062203479177686 +/- 0.001184618084040272</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>-0.004902477596204569 +/- 0.0013346324619053621</t>
+          <t>0.009857670005271536 +/- 0.0019303988849341618</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-0.005904059040590448 +/- 0.0014494177211246805</t>
+          <t>0.005587770163415951 +/- 0.0017984946873201995</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>-0.00015814443858725992 +/- 0.00024156962018747122</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>-0.000158144438587271 +/- 0.000579862941486546</t>
+          <t>0.0006325777543490063 +/- 0.0003162888771744754</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.0014232999472851727 +/- 0.0007836620320146941</t>
+          <t>-5.271481286237556e-05 +/- 0.0005503588038434759</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,52 +2156,52 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.0021085925144965325 +/- 0.0005774618423881672</t>
+          <t>0.0004744333157617353 +/- 0.0004973105499239129</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.0026357406431207543 +/- 0.001374634139209847</t>
+          <t>0.007643647865050118 +/- 0.0021509969175649134</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.00036900369003685097 +/- 0.00033753949591105656</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>-0.0011597258829731394 +/- 0.0006584078016234448</t>
+          <t>0.0004744333157617797 +/- 0.0005987251814233243</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>-0.000790722192936244 +/- 0.0009206246281799399</t>
+          <t>0.0032683183974697274 +/- 0.0012651555086979525</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.006220347917764923 +/- 0.0012869325899561182</t>
+          <t>0.0024775962045335163 +/- 0.0011799172000843087</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.001212440695835515 +/- 0.0009145678214495252</t>
+          <t>-0.00010542962572480663 +/- 0.0006584078016234341</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.005482340537691111 +/- 0.0017032677302481172</t>
+          <t>-0.0007907221929361885 +/- 0.0007907221929362181</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.005271481286241464 +/- 0.0015278204265882329</t>
+          <t>0.0030047443331576605 +/- 0.0018420037121408743</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0061676331049025255 +/- 0.0010816175291873103</t>
+          <t>0.0050606220347918065 +/- 0.001437868391880425</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.003430079155672827 +/- 0.0010619847914246975</t>
+          <t>0.00543535620052773 +/- 0.001336041044978604</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0035883905013192607 +/- 0.001023256961987603</t>
+          <t>0.006226912928759931 +/- 0.0009672982997268224</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.006596306068601565 +/- 0.0014403529355098937</t>
+          <t>0.00079155672823219 +/- 0.0011621485776013348</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0011081794195250461 +/- 0.0015376044627264933</t>
+          <t>0.0032717678100263824 +/- 0.001579591508928326</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.001635883905013169 +/- 0.001118185757277946</t>
+          <t>0.00986807387862797 +/- 0.0010567274086807977</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.0009498680738786458 +/- 0.0015971235831579466</t>
+          <t>0.009973614775725604 +/- 0.0012587715505938373</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0004221635883904895 +/- 0.00021108179419524476</t>
+          <t>0.0003693931398416783 +/- 0.00033789573812309596</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0017941952506596581 +/- 0.0012079707801857203</t>
+          <t>0.004221635883905017 +/- 0.001415979721899617</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.00026385224274404483 +/- 0.0013192612137203309</t>
+          <t>0.016728232189973623 +/- 0.0016861789243979282</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.002163588390501292 +/- 0.0014633693534419027</t>
+          <t>0.013245382585751975 +/- 0.0028067728014717214</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0025329815303429927 +/- 0.0009956708318793442</t>
+          <t>0.00543535620052773 +/- 0.0019610452956265946</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0023746701846965477 +/- 0.0014972307080856101</t>
+          <t>0.008126649076517145 +/- 0.000753712762906876</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.005171503957783608 +/- 0.000659102691123823</t>
+          <t>0.006437994722955154 +/- 0.001747012702611798</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.012559366754617418 +/- 0.0019574920307114797</t>
+          <t>0.020369393139841697 +/- 0.0036499454281352043</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.021319261213720308 +/- 0.003470033186865136</t>
+          <t>0.030870712401055413 +/- 0.003462400992575034</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0006332453825857676 +/- 0.0014120409667820251</t>
+          <t>0.00469656992084434 +/- 0.0010136872143693303</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.0013720316622691131 +/- 0.0017691878220834091</t>
+          <t>0.0048021108179419625 +/- 0.0009571692425972142</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0009498680738786236 +/- 0.0025722549038425108</t>
+          <t>0.011398416886543538 +/- 0.0018157942516184992</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0016358839050131802 +/- 0.001344352422465123</t>
+          <t>0.006596306068601609 +/- 0.0007555578397507294</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00021108179419524476 +/- 0.00025852134488476094</t>
+          <t>-5.277044854881119e-05 +/- 0.00028417756238176007</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00021108179419522256 +/- 0.0010606728887726613</t>
+          <t>0.007229551451187343 +/- 0.002017046422545281</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0024274406332453814 +/- 0.0010606728887726702</t>
+          <t>0.0004749340369393229 +/- 0.0014633693534418966</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0017941952506596026 +/- 0.000978746015355751</t>
+          <t>0.00311345646437996 +/- 0.001118185757277936</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0017414248021107915 +/- 0.0012936834482460363</t>
+          <t>-0.0022691292875989255 +/- 0.000852532687145327</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0022691292875989698 +/- 0.0010026385224274452</t>
+          <t>0.002849604221635882 +/- 0.0016384353241435325</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>5.277044854881119e-05 +/- 0.0004978354159396486</t>
+          <t>-0.00010554089709762238 +/- 0.0007000791114206452</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>-0.01261213720316624 +/- 0.0014442144784595234</t>
+          <t>0.002163588390501314 +/- 0.0023887008544076576</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.0013192612137203242 +/- 0.0015875049030597739</t>
+          <t>0.0016886543535620136 +/- 0.0011268684171009504</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-0.0032189973614775934 +/- 0.001013687214369288</t>
+          <t>0.0010026385224274458 +/- 0.001385161451019176</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.0012137203166227128 +/- 0.0010300380631104752</t>
+          <t>0.0020052770448548696 +/- 0.0013097280892866456</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0005277044854881119 +/- 0.0004719932406331878</t>
+          <t>1.1102230246251566e-17 +/- 0.001028685418977199</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0008970976253297902 +/- 0.00047493403693930073</t>
+          <t>0.00015831134564643358 +/- 0.000337895738123096</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.0029551451187335267 +/- 0.001400158222841314</t>
+          <t>-0.004274406332453818 +/- 0.0009571692425971792</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>5.277044854881119e-05 +/- 0.001067216275258898</t>
+          <t>0.0009498680738786347 +/- 0.0015257870495832167</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.0015303430079155911 +/- 0.0004383442671724936</t>
+          <t>0.0004749340369393007 +/- 0.00043834426717244553</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-0.00015831134564643358 +/- 0.0006266143581550177</t>
+          <t>-0.0003693931398416783 +/- 0.0006266143581550177</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.002796833773087093 +/- 0.0014364810120122411</t>
+          <t>-0.0008970976253298013 +/- 0.001873908274888094</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>-0.0018469656992084805 +/- 0.0008259881711081142</t>
+          <t>0.00316622691292876 +/- 0.0015475333296691618</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-1.1102230246251566e-17 +/- 0.0012033513721362791</t>
+          <t>0.0003693931398416894 +/- 0.0008525326871453029</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0022163588390501586 +/- 0.001543930220403985</t>
+          <t>0.004221635883905006 +/- 0.0016853529733690227</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0011609498680738572 +/- 0.0008766885343449164</t>
+          <t>0.004485488126649095 +/- 0.0018318263807609414</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>-0.00622691292875992 +/- 0.001870189461389911</t>
+          <t>-0.00480211081794194 +/- 0.0011905555855069542</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-0.026015831134564647 +/- 0.002030805425318603</t>
+          <t>-0.011715039577836383 +/- 0.0017786068122799651</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>-0.011345646437994716 +/- 0.0012319385255861468</t>
+          <t>-0.009023746701846936 +/- 0.003125953186199441</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.001846965699208436 +/- 0.0010878906663898966</t>
+          <t>0.007757255936675467 +/- 0.0016528189723868873</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.0014775725593667798 +/- 0.0005683551247635635</t>
+          <t>0.007757255936675455 +/- 0.001416962699957505</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.0014248021108179908 +/- 0.0005303364443863494</t>
+          <t>-0.0005804749340369231 +/- 0.00028417756238176007</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.0024274406332453593 +/- 0.0015866275861079646</t>
+          <t>0.009656992084432704 +/- 0.0013770963958522355</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.0007387862796833678 +/- 0.0013597993379129238</t>
+          <t>0.0056464379947229635 +/- 0.00193243624523488</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.004168865435356217 +/- 0.0010929981623856533</t>
+          <t>-0.020738786279683376 +/- 0.0012936834482460318</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>5.277044854881119e-05 +/- 0.0019092403709894928</t>
+          <t>-0.00875989445910289 +/- 0.00216551815606154</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.0003693931398416783 +/- 0.000337895738123096</t>
+          <t>-0.0006860158311345566 +/- 0.0008525326871453055</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.00010554089709762238 +/- 0.0007387862796833566</t>
+          <t>0.0004221635883904895 +/- 0.0006154038939150541</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.01889182058047495 +/- 0.0013515829524924092</t>
+          <t>-0.002796833773087071 +/- 0.0008525326871453207</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.006226912928759887 +/- 0.0020949269911640462</t>
+          <t>-0.007282321899736144 +/- 0.003199473644585569</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.0043799472295514615 +/- 0.001798071244052844</t>
+          <t>0.0029551451187335267 +/- 0.0013182053822476713</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,107 +2506,107 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.0008970976253298235 +/- 0.0005303364443863549</t>
+          <t>0.0006332453825857343 +/- 0.0005170426897695219</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.00153034300791558 +/- 0.0016927720245219456</t>
+          <t>0.009182058047493424 +/- 0.001905590510318493</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-0.009234828496042225 +/- 0.0012543392426390269</t>
+          <t>-0.009762532981530337 +/- 0.0016049505356987412</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.000844327176780979 +/- 0.0005381550937828646</t>
+          <t>-0.0003693931398416783 +/- 0.0006695819282558927</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.004907651715039552 +/- 0.0015839927197681897</t>
+          <t>0.013614775725593675 +/- 0.0012664907651715148</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.025646437994722958 +/- 0.0016553442893253918</t>
+          <t>-0.013773087071240109 +/- 0.0022444506932070476</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.01493403693931401 +/- 0.0023128872824075028</t>
+          <t>-0.005118733509234807 +/- 0.002150679036655914</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-0.002585751978891848 +/- 0.0008327036326152741</t>
+          <t>0.0025857519788918372 +/- 0.0008327036326152804</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.00026385224274405594 +/- 0.00026385224274405594</t>
+          <t>-0.00010554089709762238 +/- 0.00031662269129286715</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>-0.0005804749340369453 +/- 0.0008970976253298216</t>
+          <t>0.0032189973614775713 +/- 0.0011905555855069604</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.00015831134564644466 +/- 0.0008192176620717655</t>
+          <t>-0.0008970976253298013 +/- 0.0009744688819324141</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>-0.0006860158311345676 +/- 0.000748150231069028</t>
+          <t>0.004168865435356195 +/- 0.001142818355024163</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.00026385224274404483 +/- 0.001137934493553961</t>
+          <t>0.007229551451187343 +/- 0.0011330295806640449</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.0016358839050132246 +/- 0.001166931102242546</t>
+          <t>0.00395778364116095 +/- 0.001533978032057891</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.0011609498680738683 +/- 0.0012882908301565853</t>
+          <t>0.0003693931398416783 +/- 0.0010300380631104269</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.00010554089709762238 +/- 0.0003948978772320672</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0011081794195250461 +/- 0.0007985617915789728</t>
+          <t>0.0004221635883904895 +/- 0.00046004210485916115</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0008443271767810123 +/- 0.000789795754464173</t>
+          <t>-0.0005277044854881119 +/- 0.0007079898609497816</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.0004749340369393007 +/- 0.00015831134564643355</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.0007387862796833788 +/- 0.00048364914986343845</t>
+          <t>0.0014775725593667577 +/- 0.0006591026911238657</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>-0.00036939313984171165 +/- 0.0013360410449785986</t>
+          <t>-0.00026385224274405594 +/- 0.00048651949642705163</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0011081794195250349 +/- 0.0007254737247950995</t>
+          <t>-0.0007915567282321678 +/- 0.0003539949304748908</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>-0.00015831134564644466 +/- 0.0008192176620717725</t>
+          <t>0.004643799472295529 +/- 0.0013097280892866358</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.002216358839050148 +/- 0.0011513152627583934</t>
+          <t>0.00158311345646438 +/- 0.0012262744104086943</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0012137203166226573 +/- 0.0005303364443863118</t>
+          <t>-0.00021108179419525585 +/- 0.0011609498680738694</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>-0.00042216358839050063 +/- 0.0006591026911238427</t>
+          <t>0.004485488126649073 +/- 0.0009215962636713939</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.0017941952506596026 +/- 0.0009200842097183616</t>
+          <t>0.004116094986807395 +/- 0.0013720316622691173</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.00437994722955144 +/- 0.0012936834482460483</t>
+          <t>0.006596306068601609 +/- 0.00123193852558613</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.007830739299610867 +/- 0.0013132295719844311</t>
+          <t>-0.00029182879377431803 +/- 0.0009279564216118116</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.001702334630350233 +/- 0.0020083485235469845</t>
+          <t>-0.0048151750972762804 +/- 0.0020224341329077955</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0059338521400778 +/- 0.0010386262891081005</t>
+          <t>0.0005350194552529164 +/- 0.0007031533217315617</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0026264591439688623 +/- 0.0016876801140950789</t>
+          <t>0.0004863813229571967 +/- 0.0006525490206711425</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.004134241245136172 +/- 0.001948562803892029</t>
+          <t>-0.005350194552529242 +/- 0.0008700653608949003</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.002383268482490264 +/- 0.0015140449821277554</t>
+          <t>0.0012159533073929918 +/- 0.0010488258099634119</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0005836575875486361 +/- 0.000424017406959208</t>
+          <t>-0.00024319066147859836 +/- 0.00024319066147859836</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.01035992217898829 +/- 0.0016995530359587632</t>
+          <t>-0.0018482490272373475 +/- 0.0014880407140834924</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-0.031031128404669282 +/- 0.003224821878258922</t>
+          <t>-0.04571984435797671 +/- 0.0038788719917075515</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.02850194552529185 +/- 0.0030699871280271494</t>
+          <t>-0.04640077821011679 +/- 0.004000172216916734</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.009970817120622644 +/- 0.0015264936601629535</t>
+          <t>-0.001021400778210113 +/- 0.0008822158145533555</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0048151750972762475 +/- 0.0008268482490272343</t>
+          <t>0.003258754863813218 +/- 0.0010886687395719509</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.004280155642023331 +/- 0.001682063858539934</t>
+          <t>0.002091439688715946 +/- 0.0015692865568970448</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.011673151750972832 +/- 0.0020404841404088477</t>
+          <t>-0.01206225680933859 +/- 0.0019430918633694659</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.009143968871595298 +/- 0.0017237398002596584</t>
+          <t>0.005350194552529164 +/- 0.0018584604255391763</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.006274319066147838 +/- 0.0012580269607371125</t>
+          <t>-4.863813229571967e-05 +/- 0.0011396278709980487</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.005058365758754846 +/- 0.002065832741400314</t>
+          <t>0.0006322957198443557 +/- 0.0012692595671887007</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.011527237354085562 +/- 0.002005991306157705</t>
+          <t>0.0017996108949416278 +/- 0.0014271790613931087</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.006225680933852118 +/- 0.0016248339580243196</t>
+          <t>0.0016536964980544688 +/- 0.0009021029664879057</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.0013132295719844311 +/- 0.0006895645369045611</t>
+          <t>9.727626459143934e-05 +/- 0.00029182879377431803</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.008365758754863784 +/- 0.002268852877371704</t>
+          <t>-0.0014105058365758705 +/- 0.0010074083257396841</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.004620622568093369 +/- 0.0013452642690602414</t>
+          <t>-0.0012645914396887115 +/- 0.0013087182925168933</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.007538910505836549 +/- 0.0016458097583354641</t>
+          <t>0.001021400778210113 +/- 0.0010973262813889532</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0007782101167315147 +/- 0.0011133777375738868</t>
+          <t>-0.0032587548638132293 +/- 0.001306004044951141</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.004766536964980528 +/- 0.001667940486330952</t>
+          <t>-0.0025778210116731426 +/- 0.0011312941001569033</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.00019455252918287869 +/- 0.00023827721233299318</t>
+          <t>0.0005350194552529164 +/- 0.0003404669260700377</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.004280155642023331 +/- 0.0021289950027470047</t>
+          <t>-0.0027723735408560326 +/- 0.0021094599651947012</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.006468871595330716 +/- 0.0018717783467795516</t>
+          <t>0.0008268482490272344 +/- 0.0014436597353750756</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.002675097276264582 +/- 0.0017023346303501885</t>
+          <t>-4.863813229571967e-05 +/- 0.0008549803419867162</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.00038910505836575737 +/- 0.0008080373407507826</t>
+          <t>0.00043774319066147704 +/- 0.0011602004320891556</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>-0.0009727626459144045 +/- 0.0009228436751464401</t>
+          <t>-0.0015077821011673098 +/- 0.0005524229908366005</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.00038910505836575737 +/- 0.0009431283769292435</t>
+          <t>-0.0003404669260700377 +/- 0.00022288792290641168</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.010165369649805411 +/- 0.0018386243357427755</t>
+          <t>0.00029182879377431803 +/- 0.0009279564216118115</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.003550583657587536 +/- 0.002470989454451458</t>
+          <t>-0.002383268482490264 +/- 0.0012002881983709168</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.00043774319066147704 +/- 0.0003404669260700377</t>
+          <t>-9.727626459143934e-05 +/- 0.0001945525291828787</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>0.0005350194552529164 +/- 0.0006322957198443557</t>
+          <t>0.0007295719844357951 +/- 0.0003921331589639359</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.007198443579766511 +/- 0.0011260541734231697</t>
+          <t>0.0004863813229571967 +/- 0.0017671111016133159</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.004085603112840452 +/- 0.001047697433294647</t>
+          <t>-0.0014105058365758705 +/- 0.0007360284995341197</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.0028696498054474606 +/- 0.0013311218077241207</t>
+          <t>-0.0015564202334630295 +/- 0.0007148316369989794</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.008608949416342382 +/- 0.0011520154943897832</t>
+          <t>-0.004766536964980572 +/- 0.0014063066434631725</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.0017996108949416278 +/- 0.0016572689725098016</t>
+          <t>-0.0018482490272373475 +/- 0.0011468702453843924</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.0003404669260700488 +/- 0.0018074809509788165</t>
+          <t>-0.002383268482490264 +/- 0.0016486820288597501</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.016828793774319117 +/- 0.0021881754628797576</t>
+          <t>-0.010311284046692681 +/- 0.001979279177954838</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0.001605058365758727 +/- 0.003460151052885703</t>
+          <t>-0.013229571984435862 +/- 0.0018812334246900435</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.006760700389105034 +/- 0.0019388260143963696</t>
+          <t>0.002383268482490264 +/- 0.0015902512377696262</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.015856031128404613 +/- 0.002895501180182328</t>
+          <t>0.0021400778210116655 +/- 0.0008754863813229541</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.0008754863813229541 +/- 0.00019455252918287869</t>
+          <t>0.0005350194552529164 +/- 0.0006686637687192351</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.0059338521400778 +/- 0.0009678866119714166</t>
+          <t>-0.0011673151750972721 +/- 0.0010919233618990063</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>-0.010943579766537037 +/- 0.0023653339330326427</t>
+          <t>-0.013035019455252983 +/- 0.0015805522188007649</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.015710116731517565 +/- 0.0033630727457319974</t>
+          <t>-0.0333171206225681 +/- 0.0022315310791740277</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-0.01658560311284052 +/- 0.003372906312759873</t>
+          <t>-0.014299610894941694 +/- 0.002088609976029554</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.00019455252918287869 +/- 0.0008196643748226</t>
+          <t>0.0010700389105058328 +/- 0.0007782101167315147</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.00019455252918287869 +/- 0.0005836575875486361</t>
+          <t>-0.0006322957198443557 +/- 0.0005775458213539823</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0005350194552529164 +/- 0.0002619243583236617</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>-0.02402723735408563 +/- 0.00421891993038937</t>
+          <t>-0.02091439688715957 +/- 0.0027685310254392326</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.004426070038910579 +/- 0.0023065964399571</t>
+          <t>-0.023054474708171235 +/- 0.0021111414799815783</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.0006809338521400754 +/- 0.0004457758458128233</t>
+          <t>-0.0011673151750972721 +/- 0.00044577584581282335</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.0077821011673151474 +/- 0.0020404841404088477</t>
+          <t>0.0027723735408560213 +/- 0.00182052210819191</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-0.0251945525291829 +/- 0.0037662374868883018</t>
+          <t>-0.043774319066147926 +/- 0.0025552384312380644</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.00024319066147859836 +/- 0.0007295719844357951</t>
+          <t>-0.001021400778210113 +/- 0.0005077970091882546</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.005496108949416323 +/- 0.0015842896376364079</t>
+          <t>0.0035019455252918164 +/- 0.0018812334246900435</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-0.013861867704280217 +/- 0.002166991187737878</t>
+          <t>-0.02684824902723737 +/- 0.0023708283282011474</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0021887159533074407 +/- 0.0017704547396110556</t>
+          <t>-0.0027723735408560213 +/- 0.0010667175194290482</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>0.002091439688715946 +/- 0.001306004044951119</t>
+          <t>0.0014591439688715901 +/- 0.0007534987054878216</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-0.00024319066147859836 +/- 0.00032627451033557126</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.0023346303501945442 +/- 0.0014720569990682394</t>
+          <t>-0.002383268482490264 +/- 0.000934308011298564</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>-0.0007782101167315258 +/- 0.0009776143600312359</t>
+          <t>0.0016536964980544688 +/- 0.001024869042106294</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-0.0022373540856031383 +/- 0.0007279489079327168</t>
+          <t>0.0 +/- 0.0003767493527439108</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.0024319066147859836 +/- 0.001171361340349441</t>
+          <t>0.00029182879377431803 +/- 0.0005416113193414399</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0006809338521400865 +/- 0.0011344264386858693</t>
+          <t>0.00019455252918287869 +/- 0.001134426438685852</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>0.0016536964980544688 +/- 0.0005836575875486361</t>
+          <t>0.0017509727626459082 +/- 0.0008754863813229541</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.0006809338521400754 +/- 0.0004457758458128233</t>
+          <t>-0.0003404669260700377 +/- 0.00022288792290641165</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.0003404669260700377 +/- 0.0007550668626585588</t>
+          <t>-0.00038910505836575737 +/- 0.00019455252918287869</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.00029182879377431803 +/- 0.0007902761094003824</t>
+          <t>4.863813229571967e-05 +/- 0.0003404669260700377</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.00024319066147859836 +/- 0.0004983925469824689</t>
+          <t>0.00024319066147859836 +/- 0.0003921331589639359</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.012937743190661433 +/- 0.003007709111622617</t>
+          <t>0.00038910505836575737 +/- 0.0009678866119714168</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>4.863813229571967e-05 +/- 0.00014591439688715901</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0008754863813229541 +/- 0.0005238487166473235</t>
+          <t>4.863813229571967e-05 +/- 0.00014591439688715901</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>0.0009241245136186738 +/- 0.001219838152138561</t>
+          <t>-0.00019455252918287869 +/- 0.00032262887065713893</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.004085603112840452 +/- 0.0012149801553304235</t>
+          <t>0.00038910505836575737 +/- 0.0009177024447525846</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.0003404669260700377 +/- 0.000311436003766188</t>
+          <t>0.00029182879377431803 +/- 0.00032262887065713893</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0011186770428015524 +/- 0.001287762869151136</t>
+          <t>0.0024319066147859836 +/- 0.0015685326358557434</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0006809338521400643 +/- 0.001861004520399719</t>
+          <t>-0.00019455252918287869 +/- 0.000622872007532376</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.00029182879377431803 +/- 0.0010015204417302495</t>
+          <t>-0.0007782101167315147 +/- 0.0004960135713611641</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.00500736377025035 +/- 0.00107105666319447</t>
+          <t>-0.0010800196367206749 +/- 0.0014857875258146018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,92 +3111,92 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-0.016691212567501168 +/- 0.0020943278358077043</t>
+          <t>-0.021354933726067782 +/- 0.0019296263138962669</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.00903289150711828 +/- 0.0020618556701030855</t>
+          <t>-0.0009818360333824327 +/- 0.0017147029157165551</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.00039273441335296866 +/- 0.0016691212567501168</t>
+          <t>0.002356406480117812 +/- 0.0009262622613703064</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.0032891507118311125 +/- 0.001964285618433234</t>
+          <t>-0.008198330878743332 +/- 0.0010309278350515427</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.00500736377025035 +/- 0.0020688568979583114</t>
+          <t>-0.0034855179185076636 +/- 0.0008904446316749098</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.00014727540500736325 +/- 0.00031434090512679554</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.00014727540500736325 +/- 0.0015376003695008118</t>
+          <t>-0.005547373588610793 +/- 0.0010766672655601979</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.014187530682376104 +/- 0.002949187686966232</t>
+          <t>-0.00903289150711839 +/- 0.0017453499101257844</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.004958271968581241 +/- 0.0032374545103186253</t>
+          <t>0.00363279332351496 +/- 0.0017034218530090732</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.005989199803632772 +/- 0.0020454262794304943</t>
+          <t>-0.0031418753068238048 +/- 0.0011658656933763675</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0010309278350515427 +/- 0.0012114838173051567</t>
+          <t>-0.0062346588119784885 +/- 0.0015686347873019538</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.009131075110456521 +/- 0.001990489438656183</t>
+          <t>0.002945508100147265 +/- 0.001353367575070218</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.02258222876779581 +/- 0.003293178170102771</t>
+          <t>0.011880216003927302 +/- 0.002193255562463289</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.02130584192439866 +/- 0.0030830276815135053</t>
+          <t>0.028571428571428536 +/- 0.0034209624722993637</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.004860088365242987 +/- 0.001894332978063296</t>
+          <t>-0.002749140893470814 +/- 0.0007976473642254652</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.008492881688757947 +/- 0.002405498281786933</t>
+          <t>-0.008934707903780148 +/- 0.0021600392734413276</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.013696612665684893 +/- 0.0022651491399232767</t>
+          <t>0.006185567010309256 +/- 0.0015555208166671381</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0003436426116838476 +/- 0.002405498281786933</t>
+          <t>-0.005743740795287266 +/- 0.0022502045432235456</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3206,62 +3206,62 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0032891507118311125 +/- 0.002334313878835287</t>
+          <t>0.004614629356897382 +/- 0.0013390458219917337</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>-0.0009818360333824216 +/- 0.0012801575660682622</t>
+          <t>-0.005940108001963762 +/- 0.0019196087183129193</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-0.002503681885125175 +/- 0.0014800995023742055</t>
+          <t>-0.0021109474717722065 +/- 0.0004933665007914018</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>-0.004270986745213534 +/- 0.0017154055188665768</t>
+          <t>-0.0024545900834560762 +/- 0.001439654226668186</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.004712812960235624 +/- 0.00152421941053117</t>
+          <t>0.00225822287677957 +/- 0.0013209252868997213</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0007363770250368162 +/- 0.000452604047977067</t>
+          <t>0.0007363770250368162 +/- 0.0007363770250368161</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0032400589101619914 +/- 0.002356406480117812</t>
+          <t>-0.00176730486008837 +/- 0.001426199219080427</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.008443789887088826 +/- 0.0015019203280096512</t>
+          <t>-0.01261659302896423 +/- 0.0018375029231431355</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0037800687285223233 +/- 0.0018892372513395963</t>
+          <t>-0.014727540500736436 +/- 0.002000152065533951</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0002454590083456054 +/- 0.0015869641507358426</t>
+          <t>-0.0036327933235150377 +/- 0.0009105172798719735</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-9.818360333824216e-05 +/- 0.00048099945857303276</t>
+          <t>-0.0012763868433971481 +/- 0.0007976473642254229</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0034364261168384758 +/- 0.0005808620307412464</t>
+          <t>0.0007854688267059373 +/- 0.0004499337943010136</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.004909180166912108 +/- 0.0014890280695241088</t>
+          <t>-0.003976435935198886 +/- 0.0012312161221389127</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.007412862052037283 +/- 0.0023487233606098467</t>
+          <t>-0.001816396661757491 +/- 0.0009582337405961437</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.0003436426116838476 +/- 0.00022496689715050683</t>
+          <t>-0.0002454590083456054 +/- 0.0002454590083456054</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>-0.0016200294550809957 +/- 0.0011205412086905534</t>
+          <t>-0.0007363770250368162 +/- 0.000503041274715737</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.0017182130584192379 +/- 0.0012467771329602601</t>
+          <t>-0.0016200294550809957 +/- 0.0004933665007914018</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0008836524300441795 +/- 0.00230051536845556</t>
+          <t>0.00014727540500736325 +/- 0.0011205412086905534</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0033873343151693547 +/- 0.0008904446316748645</t>
+          <t>-4.909180166912108e-05 +/- 0.0005992418073506951</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0007281490905346723</t>
+          <t>0.0013745704467353903 +/- 0.0006131564063228646</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0037309769268532023 +/- 0.0017314867048157424</t>
+          <t>-0.003681885125184148 +/- 0.0014270438737112468</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.00044182621502208974 +/- 0.0013963144480439707</t>
+          <t>-0.0016200294550809957 +/- 0.0010072795546727108</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.004369170348551776 +/- 0.0013254786450662692</t>
+          <t>-0.0008345606283750584 +/- 0.0009830625623220774</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.0009327442317133006 +/- 0.0031237974020486945</t>
+          <t>-0.01084928816887587 +/- 0.00117102213469578</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.005252822778595956 +/- 0.0011833059198030347</t>
+          <t>0.00039273441335296866 +/- 0.0007854688267059373</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.003092783505154628 +/- 0.002117786412383202</t>
+          <t>-0.003878252331860643 +/- 0.0008345606283751022</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0002945508100147265 +/- 0.0005466631676809035</t>
+          <t>-0.00039273441335296866 +/- 0.0003673694046906164</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.0038291605301914444 +/- 0.0015647891458526431</t>
+          <t>-0.0016691212567501168 +/- 0.0009366118816072087</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.012027491408934665 +/- 0.0017182130584192379</t>
+          <t>-0.012812960235640714 +/- 0.0017487985400644883</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.002405498281786933 +/- 0.0012697611346467862</t>
+          <t>0.004761904761904745 +/- 0.0012035003114512733</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.0068237604320078304 +/- 0.00167848021573674</t>
+          <t>-0.005596465390279903 +/- 0.002294221196965728</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.00044182621502208974 +/- 0.0005992418073506951</t>
+          <t>4.909180166912108e-05 +/- 0.0003436426116838476</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.0019636720667648433 +/- 0.0007281490905346723</t>
+          <t>-0.00019636720667648433 +/- 0.00032563817283803517</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.005252822778595956 +/- 0.0012997744030312892</t>
+          <t>0.003534609720176718 +/- 0.0007854688267059373</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.006332842415316642 +/- 0.00222218366180784</t>
+          <t>0.0062346588119783775 +/- 0.0018505720986716444</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.005301914580265077 +/- 0.001093326335361807</t>
+          <t>-0.0006381934216985851 +/- 0.001687073174024527</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0019145802650957222 +/- 0.0009430227153803867</t>
+          <t>-0.0023564064801178232 +/- 0.0004809994585730577</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.004663721158566503 +/- 0.0015091238241472108</t>
+          <t>-0.0006381934216985741 +/- 0.0014066321828074967</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0050564555719194715 +/- 0.0016582568241585152</t>
+          <t>-0.0018163966617575022 +/- 0.001811081663789587</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.003043691703485507 +/- 0.0009262622613703063</t>
+          <t>-0.0004909180166912108 +/- 0.00021954521134018475</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.005203730976926835 +/- 0.0025147272410143647</t>
+          <t>0.0009818360333824216 +/- 0.0013172712680411085</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.0027982326951399017 +/- 0.0013719380080983868</t>
+          <t>0.0013745704467353903 +/- 0.0015647891458526431</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.013892979872361377 +/- 0.0017570476355594715</t>
+          <t>0.004221894943544413 +/- 0.0017591038652104915</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.00363279332351496 +/- 0.0014429983757190982</t>
+          <t>-0.016445753559155674 +/- 0.0019420756450517834</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.00019636720667648433 +/- 0.00039273441335296866</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.00500736377025035 +/- 0.001001280218673101</t>
+          <t>-0.0018654884634266122 +/- 0.0011365573787717614</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.005154639175257714 +/- 0.000452604047977067</t>
+          <t>0.0003436426116838476 +/- 0.0009830625623220772</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0006381934216985741 +/- 0.0010540456825519791</t>
+          <t>-0.0020127638684339644 +/- 0.0005575756844182871</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.00407461953853705 +/- 0.0005400098183603319</t>
+          <t>-0.0074128620520373945 +/- 0.0009171105396303062</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0010800196367206638 +/- 0.0011984836147013902</t>
+          <t>0.00039273441335296866 +/- 0.0007214991878595492</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.020029455081001422 +/- 0.0017943708279329724</t>
+          <t>-0.0035837015218459166 +/- 0.0011627608524621888</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-0.0004909180166912108 +/- 0.0</t>
+          <t>-0.00014727540500736325 +/- 0.00022496689715050683</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>0.0016200294550809957 +/- 0.0010309278350515427</t>
+          <t>0.0010309278350515427 +/- 0.0005575756844182871</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.004123711340206171 +/- 0.0012650072387555306</t>
+          <t>0.00039273441335296866 +/- 0.00019636720667648433</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.0002454590083456054 +/- 0.00039579075838480713</t>
+          <t>0.00044182621502208974 +/- 0.00026436744266737774</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-0.0028473244968090228 +/- 0.0014194238875602267</t>
+          <t>-0.001227295041728027 +/- 0.0006305956101455613</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>9.818360333824216e-05 +/- 0.0007854688267059373</t>
+          <t>0.001129111438389785 +/- 0.0006604626434498607</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.0015709376534118746 +/- 0.0009769145185141055</t>
+          <t>-0.0010309278350515427 +/- 0.001129111438389785</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0068728522336769515 +/- 0.001353367575070218</t>
+          <t>-0.0009327442317133006 +/- 0.0008629551218088799</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>0.002503681885125175 +/- 0.0008629551218088799</t>
+          <t>0.0002454590083456054 +/- 0.000452604047977067</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.005154639175257714 +/- 0.001357812143931201</t>
+          <t>0.0010800196367206638 +/- 0.00048099945857303276</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.007511045655375526 +/- 0.0013542576557814111</t>
+          <t>0.0038782523318605655 +/- 0.0007097119437801133</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>0.0007363770250368162 +/- 0.0012659594460704548</t>
+          <t>0.006774668630338709 +/- 0.0008446072918058513</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.0038310412573674068 +/- 0.000952392899295957</t>
+          <t>0.005500982318271064 +/- 0.0014201210505698169</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.009921414538310424 +/- 0.001277013752455791</t>
+          <t>0.008742632612966561 +/- 0.0015026580098996389</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-9.823182711197199e-05 +/- 0.0012190249161091388</t>
+          <t>-0.0002455795677799966 +/- 0.0015414886862942234</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.0014734774066797573 +/- 0.0010534189876978237</t>
+          <t>0.00039292730844792123 +/- 0.0011156990856189047</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0005402750491159347 +/- 0.000890881981690431</t>
+          <t>0.00014734774066794688 +/- 0.0009332023575638465</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.004076620825147348 +/- 0.0012040914216239003</t>
+          <t>0.0025540275049115934 +/- 0.0011371156093114242</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-9.823182711197199e-05 +/- 0.000196463654223944</t>
+          <t>0.0006385068762278622 +/- 0.0004420432220039208</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.006630648330058941 +/- 0.0007367387033398601</t>
+          <t>0.011100196463654188 +/- 0.0016021126159430409</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.005451866404715155 +/- 0.0032613114540341794</t>
+          <t>-0.0009823182711198419 +/- 0.002504430016499401</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.003192534381139522 +/- 0.004470627473899255</t>
+          <t>-0.00437131630648332 +/- 0.002527919299107611</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.00024557956777997435 +/- 0.0011674719375250383</t>
+          <t>0.0019155206286836646 +/- 0.0017496574784437154</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.00029469548133591593 +/- 0.0005008860032998832</t>
+          <t>0.004862475442043201 +/- 0.0013970002606412564</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.0026031434184676018 +/- 0.0011633319530773218</t>
+          <t>0.0025049115913555854 +/- 0.0014644451390840448</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-0.003045186640471498 +/- 0.0016407949988693367</t>
+          <t>-0.012475442043222018 +/- 0.0023058339085079765</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.011886051080550108 +/- 0.0031434184675835216</t>
+          <t>0.0051080550098231425 +/- 0.0038436144492168486</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.007023575638506885 +/- 0.0010771960805236417</t>
+          <t>0.009528487229862447 +/- 0.00206286836935166</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.0025540275049115934 +/- 0.0016985870791542746</t>
+          <t>0.003683693516699382 +/- 0.0021324453188695937</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>9.823182711201638e-05 +/- 0.0008450221283931776</t>
+          <t>0.00255402750491156 +/- 0.002194332799969406</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.005108055009823198 +/- 0.0011869396830643092</t>
+          <t>0.0004911591355599044 +/- 0.0020369785219378975</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4.911591355600819e-05 +/- 0.000407987419593212</t>
+          <t>0.0019155206286836646 +/- 0.0007432586419657042</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.002308447937131619 +/- 0.0014243614931237795</t>
+          <t>-0.0005402750491159125 +/- 0.0011296660117878004</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.002897838899803529 +/- 0.0009175609868501783</t>
+          <t>-0.002848722986247554 +/- 0.0014701993661194342</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>-0.0028978388998035175 +/- 0.0011081055179448253</t>
+          <t>-0.002013752455795681 +/- 0.0015755417418807042</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0016208251473477375 +/- 0.0007624840224096368</t>
+          <t>-0.0013752455795677855 +/- 0.0006515962260030292</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.0029469548133595146 +/- 0.0009319089371812399</t>
+          <t>-0.0015225933202357655 +/- 0.0010173042817882188</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.00034381139489196854 +/- 0.00031449529653403905</t>
+          <t>-0.0004911591355599487 +/- 0.00031063631239374665</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-0.0027996070726915233 +/- 0.001687901795426286</t>
+          <t>-0.005058939096267201 +/- 0.0017302470485077112</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0.001964636542239695 +/- 0.0015058653945732843</t>
+          <t>-0.002013752455795692 +/- 0.001575541741880704</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>0.004469548133595303 +/- 0.0018952633970112688</t>
+          <t>0.005157170923379151 +/- 0.0012854864762575908</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.0015717092337917404 +/- 0.0009267172035418995</t>
+          <t>0.0007858546168958425 +/- 0.0010579891566079456</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>-0.0005402750491158792 +/- 0.00034381139489194474</t>
+          <t>-0.0013752455795677965 +/- 0.0011990722608775936</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.0004420432220038961 +/- 0.0003438113948919368</t>
+          <t>-9.823182711201638e-05 +/- 0.0005727850584327376</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.00481335952848726 +/- 0.0008159748391864321</t>
+          <t>0.0017190569744597096 +/- 0.0018146319451779003</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.002357563850687594 +/- 0.0016843249704795974</t>
+          <t>0.0018172888015716925 +/- 0.0026362940865068125</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0003438113948919574 +/- 0.0003836075479325486</t>
+          <t>-0.0011296660117878442 +/- 0.0004936088222554344</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.0003929273084479101 +/- 0.00042818260742050077</t>
+          <t>-0.0021119842829076863 +/- 0.0007934918674559801</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.0016208251473477486 +/- 0.0010314341846758396</t>
+          <t>-0.0002455795677799966 +/- 0.0012473894989391088</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.002259332023575622 +/- 0.0012269151273867367</t>
+          <t>0.003241650294695453 +/- 0.001690044256786374</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.0006385068762279067 +/- 0.0003836075479325358</t>
+          <t>-0.00024557956777998546 +/- 0.0008577725538591749</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.0017681728880157067 +/- 0.0007350996830597223</t>
+          <t>-0.0035363457760314463 +/- 0.001137115609311408</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.003045186640471531 +/- 0.0011787819253438107</t>
+          <t>0.0014734774066797352 +/- 0.001850829438253137</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.0015225933202357655 +/- 0.0008908819816904066</t>
+          <t>0.0004420432220039072 +/- 0.001129666011787824</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.008055009823182724 +/- 0.0009872176445109141</t>
+          <t>4.911591355597489e-05 +/- 0.0011081055179448253</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.005157170923379151 +/- 0.001572476482670157</t>
+          <t>-0.01493123772102165 +/- 0.001375245579567775</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0015717092337917404 +/- 0.0006876227897838721</t>
+          <t>-0.006041257367387054 +/- 0.0012040914216239083</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0022593320235756442 +/- 0.0009872176445108877</t>
+          <t>0.002996070726915501 +/- 0.0012892342581931812</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3.3306690738754695e-17 +/- 0.0003804502304722367</t>
+          <t>-0.000687622789783926 +/- 0.0003257981130014987</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0008840864440078811 +/- 0.0005727850584327299</t>
+          <t>-0.002897838899803562 +/- 0.0011715972929151922</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.003732809430255424 +/- 0.0010349365179619693</t>
+          <t>-0.0034381139489194855 +/- 0.0011828678368165267</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0033398821218074805 +/- 0.001403031125450464</t>
+          <t>0.0038801571709233596 +/- 0.0009933078789860768</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.008497053045186664 +/- 0.0022080321014724055</t>
+          <t>-0.0012278978388998384 +/- 0.0022427210327761933</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.00014734774066793577 +/- 0.0006607870357108859</t>
+          <t>-0.0008349705304518951 +/- 0.0003836075479325358</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.00034381139489197965 +/- 0.0003836075479325429</t>
+          <t>4.911591355595268e-05 +/- 0.0005127851919896942</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0009332023575638448 +/- 0.00014734774066795797</t>
+          <t>-0.0011296660117878442 +/- 0.00038360754793254856</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.0023575638506876384 +/- 0.0018869717792041876</t>
+          <t>-0.00034381139489196854 +/- 0.0027526829605504974</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.0048133595284872484 +/- 0.0015808916443448991</t>
+          <t>-0.009037328094302587 +/- 0.0009370719070893308</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,77 +3841,77 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.00019646365422398837 +/- 0.0006662406663187903</t>
+          <t>9.823182711196087e-05 +/- 0.0004281826074204983</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0004911591355599044 +/- 0.0009056526971800549</t>
+          <t>0.0020137524557956588 +/- 0.0011920099311897685</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>0.0015717092337917515 +/- 0.0008450221283931595</t>
+          <t>0.008202357563850649 +/- 0.000958704385851816</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.0005893909626718763 +/- 0.0007218535587769772</t>
+          <t>-0.00039292730844796563 +/- 0.0005289945783039785</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.00103143418467585 +/- 0.001040747549136388</t>
+          <t>0.0016699410609037012 +/- 0.0010113585600183648</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>0.0005402750491159236 +/- 0.0006752321750917074</t>
+          <t>-0.004567779960707308 +/- 0.0013900758053128634</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.006532416502946925 +/- 0.0016735486284283727</t>
+          <t>-0.01797642436149316 +/- 0.002610084529584761</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.0007367387033398676 +/- 0.0007995491451915432</t>
+          <t>-0.005550098231827128 +/- 0.0011210915727419672</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4.911591355600819e-05 +/- 0.0002644972891519934</t>
+          <t>-4.91159135560193e-05 +/- 0.0005578495428094528</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>4.91159135560193e-05 +/- 0.0009434858896020912</t>
+          <t>-0.0006876227897839038 +/- 0.0008277160877383434</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.0024557956777996105 +/- 0.0009823182711198365</t>
+          <t>-0.001817288801571737 +/- 0.0010314341846758533</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0026031434184676018 +/- 0.0008521292521069551</t>
+          <t>-0.0026031434184676126 +/- 0.0008233327413674095</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.004715127701375221 +/- 0.0010349365179619418</t>
+          <t>-0.01114931237721024 +/- 0.0008799839325721635</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.0005893909626719318 +/- 0.0006134575636933554</t>
+          <t>-0.004322200392927344 +/- 0.0011581361613508426</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.0016208251473477375 +/- 0.0011210915727419904</t>
+          <t>-0.003536345776031469 +/- 0.0011581361613508378</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.00029469548133597144 +/- 0.0004501547833944754</t>
+          <t>-0.00034381139489197965 +/- 0.0009069835615235409</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.0005893909626719096 +/- 0.00042818260742049063</t>
+          <t>-0.0021119842829076642 +/- 0.0003836075479325671</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.0008349705304518396 +/- 0.00031449529653406166</t>
+          <t>-0.0029960707269155672 +/- 0.0007100605252849089</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.000785854616895898 +/- 0.0010349365179619418</t>
+          <t>-0.007711198428290811 +/- 0.0013004127991035116</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>4.911591355600819e-05 +/- 0.00026449728915199335</t>
+          <t>-0.004616895874263294 +/- 0.0004501547833944754</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0017681728880157177 +/- 0.0009624714117026224</t>
+          <t>-0.011935166994106105 +/- 0.0008799839325721683</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0004420432220039516 +/- 0.001040747549136388</t>
+          <t>-0.004273084479371336 +/- 0.001281727735825129</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0011296660117878221 +/- 0.0005402750491159276</t>
+          <t>-0.00191552062868372 +/- 0.0009933078789860887</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.0016208251473477375 +/- 0.000660787035710886</t>
+          <t>0.0037819253438113763 +/- 0.0015383555759691451</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.0011787819253438303 +/- 0.0007672150958650972</t>
+          <t>-0.0005893909626719429 +/- 0.000785854616895873</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.001964636542239695 +/- 0.00126181066588065</t>
+          <t>-0.002111984282907675 +/- 0.000852129252106973</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.0005838641188960047 +/- 0.0010468727666303542</t>
+          <t>0.0027070063694267787 +/- 0.0005007420983044994</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.003662420382165588 +/- 0.0012436703305583833</t>
+          <t>0.0033970276008492895 +/- 0.001960316912167662</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.007484076433121001 +/- 0.0008032243073472209</t>
+          <t>0.00037154989384291515 +/- 0.0012115405743644756</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0020700636942674764 +/- 0.001288180583812258</t>
+          <t>0.0009554140127388977 +/- 0.0006629509552439894</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.004405520169851329 +/- 0.0015392781316348149</t>
+          <t>-0.00037154989384285964 +/- 0.0013012368017124537</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.00031847133757959554 +/- 0.0026666362392952234</t>
+          <t>0.0006900212314225329 +/- 0.0017771410873442966</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.00010615711252655035 +/- 0.0002123142250531007</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.005891719745222934 +/- 0.0018455773514558138</t>
+          <t>0.0013269639065817684 +/- 0.001631680058273829</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.011464968152866262 +/- 0.0021124998664684013</t>
+          <t>0.024416135881104063 +/- 0.002028128787106457</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.009129511677282398 +/- 0.002025348622965921</t>
+          <t>0.02691082802547775 +/- 0.001899737809784853</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.0011146496815286344 +/- 0.0006900212314225116</t>
+          <t>0.00419320594479834 +/- 0.0016692340969762574</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.0023885350318471055 +/- 0.0013269639065817572</t>
+          <t>0.005201698513800456 +/- 0.0011334477974555507</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.0017515923566879255 +/- 0.001211540574364478</t>
+          <t>0.0019108280254777287 +/- 0.0007944070884870495</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0066348195329087424 +/- 0.0018116823955282412</t>
+          <t>0.003927813163481985 +/- 0.0014083332443122624</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002441613588110425 +/- 0.0023997143429845694</t>
+          <t>0.008280254777070095 +/- 0.0018417570671865622</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.0021762208067940937 +/- 0.0017354334102199279</t>
+          <t>0.0007961783439490832 +/- 0.0015790312930619376</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.004989384288747389 +/- 0.0019313593841465276</t>
+          <t>0.010881104033970301 +/- 0.0014093331260458261</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.0016985138004246502 +/- 0.0013173751216550783</t>
+          <t>-0.0028131634819532625 +/- 0.0008897587374862156</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.0033439490445860143 +/- 0.0013851367675902161</t>
+          <t>0.016082802547770735 +/- 0.002028823232867998</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00023737451990443623</t>
+          <t>-0.00010615711252652816 +/- 0.0002123142250530563</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.008227176220806764 +/- 0.0011927922003314407</t>
+          <t>-0.0015923566878980554 +/- 0.0008222894577935137</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0013269639065817684 +/- 0.0013687682545889337</t>
+          <t>-0.00015923566878978113 +/- 0.0003398685900972719</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-0.000530785562632663 +/- 0.00047474903980888487</t>
+          <t>0.0020169851380042792 +/- 0.0009131980113633334</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.00037154989384291515 +/- 0.0011146496815286557</t>
+          <t>0.0010084925690021507 +/- 0.0006900212314225116</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.0021231422505308185 +/- 0.001186872599522176</t>
+          <t>0.0007961783439490611 +/- 0.0009568872811740962</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.0005307855626326518 +/- 0.00023737451990443623</t>
+          <t>-0.0002123142250530563 +/- 0.00026003075825721035</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0044055201698513955 +/- 0.0014053293306659923</t>
+          <t>0.0013269639065817684 +/- 0.0008640562949097455</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.0021231422505307517 +/- 0.0015199385417490935</t>
+          <t>0.0004777070063694544 +/- 0.001309868649602237</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0007430997876858081 +/- 0.001191610632730568</t>
+          <t>5.307855626330848e-05 +/- 0.0005541563964389796</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0023354564755838194 +/- 0.001367738718336003</t>
+          <t>0.0015923566878980999 +/- 0.0013001537912861831</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.00010615711252655035 +/- 0.0002123142250531007</t>
+          <t>0.0002653927813163759 +/- 0.0002653927813163759</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.0002653927813163315 +/- 0.0003560617798566419</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,122 +4161,122 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.00021231422505311182 +/- 0.0016134484239459256</t>
+          <t>0.004511677282377946 +/- 0.001631680058273829</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0009023354564755448 +/- 0.00185471392883823</t>
+          <t>0.001592356687898111 +/- 0.000855866003004099</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.00010615711252655035 +/- 0.0002123142250531007</t>
+          <t>-0.0002653927813163204 +/- 0.0002653927813163204</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.000530785562632663 +/- 0.0003356982654106559</t>
+          <t>-0.00047770700636937666 +/- 0.0001592356687897922</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.002441613588110447 +/- 0.0012150236881379739</t>
+          <t>0.00015923566878984775 +/- 0.0006302729345561568</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>0.0019639065817409927 +/- 0.0014833533558898213</t>
+          <t>0.006528662420382192 +/- 0.0013438417092539437</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.00015923566878978113 +/- 0.00047770700636942974</t>
+          <t>0.0002653927813163648 +/- 0.00035606177985666673</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.0004777070063693989 +/- 0.0012208067940552001</t>
+          <t>0.0018577494692144647 +/- 0.0011445784847583858</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.00010615711252651706 +/- 0.001570981803285445</t>
+          <t>0.0031316348195329136 +/- 0.0009627578103618364</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0028662420382165933 +/- 0.0009254562512825067</t>
+          <t>0.0007430997876858081 +/- 0.00026003075825721035</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.0004777070063694544 +/- 0.0014331210191082687</t>
+          <t>0.0013800424628450324 +/- 0.0020721041715438503</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.006475583864118862 +/- 0.0010292313922327524</t>
+          <t>-0.003397027600849234 +/- 0.0008624244590908716</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.00042462845010612373 +/- 0.0008818072041314262</t>
+          <t>-0.00037154989384287075 +/- 0.0007140989409274836</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0019639065817409597 +/- 0.0007890694664181949</t>
+          <t>0.0016454352441613862 +/- 0.0006900212314225116</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.00042462845010612373 +/- 0.0005716735464049304</t>
+          <t>-5.307855626326408e-05 +/- 0.0001592356687897922</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>0.0005838641188959937 +/- 0.000837565490342866</t>
+          <t>0.00015923566878983664 +/- 0.0011146496815286557</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.002123142250530807 +/- 0.0013001537912861786</t>
+          <t>0.00674097664543527 +/- 0.0014252358367407073</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.003980891719745194 +/- 0.0014093331260458346</t>
+          <t>-0.0029193205944797905 +/- 0.0012161825092770115</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.010562632696390628 +/- 0.0017191225839385939</t>
+          <t>-0.012261146496815322 +/- 0.0011975068123862482</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.0008492569002123473 +/- 0.0003520833110780544</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.00031847133757959554 +/- 0.0003520833110780545</t>
+          <t>-5.307855626326408e-05 +/- 0.0001592356687897922</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.0038216560509554353 +/- 0.000618997016437926</t>
+          <t>-5.307855626323077e-05 +/- 0.0006479063490304499</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.01528662420382162 +/- 0.002146894736322369</t>
+          <t>-0.0002123142250530563 +/- 0.0011433470928098825</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.00031847133757965105 +/- 0.0013677387183359967</t>
+          <t>0.006528662420382181 +/- 0.0012794024196596504</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4286,42 +4286,42 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0006900212314224774 +/- 0.0005838641188959533</t>
+          <t>-0.0003184713375795845 +/- 0.00026003075825721035</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>0.0013800424628450437 +/- 0.0011916106327305603</t>
+          <t>0.00047770700636947663 +/- 0.0003715498938428786</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>0.0014331210191083077 +/- 0.0009509805131193552</t>
+          <t>-0.0004777070063693989 +/- 0.0011247144426972857</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>-0.0004246284501061348 +/- 0.0005200615165144592</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.004511677282377946 +/- 0.0014487626394857989</t>
+          <t>0.005201698513800456 +/- 0.0011821155759724165</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.008386411889596568 +/- 0.0013594743603891454</t>
+          <t>0.003343949044586003 +/- 0.0015574735404587344</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.007855626326963882 +/- 0.0010825943765589807</t>
+          <t>-0.00037154989384285964 +/- 0.0010628972608545965</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>0.004564755838641232 +/- 0.0006797371801945837</t>
+          <t>0.022983014861995766 +/- 0.0013646454492762783</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4331,32 +4331,32 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.0012208067940551626 +/- 0.0012345757271351363</t>
+          <t>0.007377919320594506 +/- 0.0018147899147854295</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.008704883227176241 +/- 0.0009844605621545403</t>
+          <t>0.0038747346072186884 +/- 0.0009509805131193681</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.00010615711252652816 +/- 0.000397203544243521</t>
+          <t>0.0006369426751592578 +/- 0.0003972035442435122</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>0.004511677282377957 +/- 0.0012616628794060191</t>
+          <t>0.0010615711252654147 +/- 0.0008222894577935137</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>0.005201698513800456 +/- 0.0014003084881393823</t>
+          <t>0.008704883227176241 +/- 0.0014083332443122639</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>0.011199575371549919 +/- 0.0010734473681611758</t>
+          <t>0.0064755838641189275 +/- 0.0010825943765589634</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>0.0004777070063694655 +/- 0.0004409036020657065</t>
+          <t>0.0002653927813163759 +/- 0.0002653927813163759</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.00031847133757965105 +/- 0.0002600307582572647</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>0.00010615711252656145 +/- 0.0005716735464049429</t>
+          <t>0.0005307855626327296 +/- 0.0003356982654106559</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.01040339702760088 +/- 0.0016480015601125365</t>
+          <t>0.0074840764331210565 +/- 0.0010993797864760134</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-5.307855626326408e-05 +/- 0.0001592356687897922</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00023737451990443623</t>
+          <t>0.0019108280254777287 +/- 0.0007944070884870348</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>0.003184713375796189 +/- 0.0010877867055158806</t>
+          <t>0.015074309978768597 +/- 0.0010401230330289513</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0049893842887473675 +/- 0.0009554140127388668</t>
+          <t>0.006740976645435282 +/- 0.0011396449338420323</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.00010615711252655035 +/- 0.0002123142250531007</t>
+          <t>0.0002123142250531007 +/- 0.0002600307582572647</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>0.006104033970276024 +/- 0.0008960691622152087</t>
+          <t>0.002016985138004268 +/- 0.00074309978768577</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>0.00605095541401276 +/- 0.001066865777189044</t>
+          <t>0.0131634819532909 +/- 0.0013385902561484579</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.005732484076433153 +/- 0.00110831279287797</t>
+          <t>-0.0022823779193205662 +/- 0.0008897587374861923</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0020066889632106453 +/- 0.0010202654803660924</t>
+          <t>-0.001433349259436245 +/- 0.0014491878536171054</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.001003344481605295 +/- 0.0018312248348530112</t>
+          <t>-0.002484472049689479 +/- 0.0009014793246112296</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.00468227424749158 +/- 0.0014772694537735598</t>
+          <t>-0.0006211180124224058 +/- 0.0011516455607447715</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.4408920985006264e-17 +/- 0.002360074349780888</t>
+          <t>-0.002818920210224596 +/- 0.0018312248348530142</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0017677974199712843 +/- 0.0013180233372320853</t>
+          <t>-0.0032489249880554793 +/- 0.001126595902776081</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0002866698518871891 +/- 0.000936259815683977</t>
+          <t>0.0012900143334925729 +/- 0.0012829165391397776</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.00014333492594366116 +/- 0.0003059304461267868</t>
+          <t>-0.00023889154323939455 +/- 0.0004404942406733615</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.00888676540850446 +/- 0.0023131807810626327</t>
+          <t>0.0003822264691829669 +/- 0.0005571860386856457</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0326325848064978 +/- 0.002408424875514285</t>
+          <t>0.05398948877209744 +/- 0.0031548158660714963</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.03024366937410411 +/- 0.0031839860643184275</t>
+          <t>0.04515050167224077 +/- 0.004231820573646504</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0045389393215479745 +/- 0.001865802598162124</t>
+          <t>0.0037744863831820075 +/- 0.0017548368535314767</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.0012422360248446785 +/- 0.0011143720773712953</t>
+          <t>0.0019589106545628175 +/- 0.0011982738847572442</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0015766841853797954 +/- 0.0016419340924452522</t>
+          <t>-0.0023889154323937455 +/- 0.0027446548717334103</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.009603440038222588 +/- 0.0019164998681444419</t>
+          <t>0.013855709507883373 +/- 0.002027061962312136</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.015050167224080225 +/- 0.005527642654288674</t>
+          <t>0.0341137123745819 +/- 0.005832868595138793</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.004777830864787313 +/- 0.0016272705557502372</t>
+          <t>0.003153368370759635 +/- 0.0013206187253784255</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.0027233635929287516 +/- 0.001613888748595739</t>
+          <t>-0.002341137123745862 +/- 0.0009895993873486736</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.004586717630195946 +/- 0.0009603321185973068</t>
+          <t>-0.003153368370759724 +/- 0.0022225902244840793</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.009603440038222588 +/- 0.0018061211821725409</t>
+          <t>0.0021022455805064233 +/- 0.001513901530602488</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.0002866698518872335 +/- 0.00023406495392098374</t>
+          <t>-0.00014333492594365005 +/- 0.00021894771595588867</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.0036311514572383574 +/- 0.0011935017674913385</t>
+          <t>0.008170090778786387 +/- 0.0022858812640049217</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.0032489249880553682 +/- 0.0012049230972688554</t>
+          <t>0.0025800286669851458 +/- 0.0013032185090287552</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.00028666985188727787 +/- 0.000983815589200873</t>
+          <t>-0.0023889154323937455 +/- 0.0013343755416884027</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0009077878643096393 +/- 0.0014404981778959648</t>
+          <t>0.0007644529383659338 +/- 0.00098381558920086</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.00043000477783091686 +/- 0.0009895993873486977</t>
+          <t>4.777830864782784e-05 +/- 0.0017020079436748212</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>4.777830864782784e-05 +/- 0.0009662564938440976</t>
+          <t>4.777830864787225e-05 +/- 0.00014333492594361676</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.0034400382226468795 +/- 0.0017463609061153284</t>
+          <t>0.002866698518872379 +/- 0.002251164642023847</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.009125656951743843 +/- 0.0018682479499299702</t>
+          <t>0.0032967032967032516 +/- 0.0022758729792287788</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>0.004013377926421357 +/- 0.002636046674464176</t>
+          <t>-0.001385570950788395 +/- 0.0009662564938440729</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0034400382226468574 +/- 0.0013479919713010892</t>
+          <t>-0.0006688963210703003 +/- 0.0015584812642427098</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.7778308647850044e-05 +/- 0.00039687643874431003</t>
+          <t>-0.0005733397037745447 +/- 0.0004681299078420083</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.0004777830864787225 +/- 0.00030217655615559215</t>
+          <t>-0.0014333492594362784 +/- 0.0004273421839464336</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,217 +4606,217 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.003965599617773474 +/- 0.0015266646257688107</t>
+          <t>-0.001720019111323501 +/- 0.0012311608912303118</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.0048733874820831025 +/- 0.0016523283770464045</t>
+          <t>0.0034878165312947516 +/- 0.0026347473825059295</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.00014333492594361674 +/- 0.0002189477159558378</t>
+          <t>-0.0003822264691830557 +/- 0.00028666985188727787</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0003344481605351057 +/- 0.00037316051963241233</t>
+          <t>0.0004300047778308391 +/- 0.0004988201867611381</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.0010511227902532672 +/- 0.0012049230972688491</t>
+          <t>0.0008600095556616893 +/- 0.000997640373522256</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.013521261347348245 +/- 0.0021478993591007305</t>
+          <t>-0.004443382704252308 +/- 0.0021265373229114007</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.00028666985188722236 +/- 0.000437895431911695</t>
+          <t>-0.000955566172957556 +/- 0.00037008918740633404</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.0004777830864787891 +/- 0.000854684367892917</t>
+          <t>0.0014333492594361674 +/- 0.0006043531123111843</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0010033444816053172 +/- 0.0009895993873486515</t>
+          <t>0.0010989010989010395 +/- 0.0009803289311363288</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0009077878643096393 +/- 0.0014562590209391433</t>
+          <t>0.0025800286669851345 +/- 0.0014834376202828453</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.0012422360248446785 +/- 0.0017120375410576909</t>
+          <t>0.0011944577161968062 +/- 0.001514655277988289</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.0021500238891543843 +/- 0.0011751910058527331</t>
+          <t>0.0012900143334925618 +/- 0.0008822831014151543</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0044911610129001025 +/- 0.000487245056243919</t>
+          <t>0.0009555661729574227 +/- 0.0011896702912554884</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0014811275680840397 +/- 0.0006907229954515275</t>
+          <t>-0.0014333492594362674 +/- 0.0014173336812414116</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
+          <t>9.555661729573339e-05 +/- 0.0003575401229597707</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0003344481605350724 +/- 0.0007417188101414434</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.00019111323459144458 +/- 0.0018155757286192112</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.005972288580984209 +/- 0.0010302846943549004</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>0.016005733397037692 +/- 0.00216061520393599</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>0.000764452938365956 +/- 0.000382226469182978</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.0004777830864787225 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0006688963210702004 +/- 0.0005733397037744892</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>0.010941232680363067 +/- 0.0021415131228872393</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-0.00023889154323941675 +/- 0.001765212919437291</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>9.555661729573339e-05 +/- 0.0002866698518872557</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>0.0010033444816053062 +/- 0.0019519061840244218</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>-0.0005255613951266503 +/- 0.0013756502674522914</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.0014811275680840397 +/- 0.000583208581735943</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.00047778308647870025 +/- 0.0007704020781938428</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>0.010129001433349216 +/- 0.00227938087756837</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>0.006306736741519314 +/- 0.0021238519609071012</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-0.004968944099378947 +/- 0.0010511227902532127</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>-0.0073578595317726255 +/- 0.0011546149998657052</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>-0.0008122312470138949 +/- 0.0019236332670040709</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>0.0004777830864787225 +/- 0.00037008918740633404</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>-0.004968944099378936 +/- 0.0008600095556617005</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>-0.005494505494505553 +/- 0.0012686018201004926</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-0.004921165790731053 +/- 0.0014499752418054039</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
           <t>-4.777830864788335e-05 +/- 0.00014333492594365005</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>0.0019589106545627845 +/- 0.0010779277756978877</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>-0.0035355948399427017 +/- 0.0019606578622726463</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>0.007740086000955515 +/- 0.002348438743897669</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>0.02250358337314855 +/- 0.003641509605789041</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-0.00023889154323941675 +/- 0.00023889154323941675</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>-0.0008122312470139281 +/- 0.0007417188101414263</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>-0.00014333492594367225 +/- 0.00037316051963246204</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0.010606784519827939 +/- 0.0020583525301995174</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-0.0003344481605351612 +/- 0.0014019494267674352</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>4.7778308647861144e-05 +/- 0.00033444816053512317</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>-0.004443382704252308 +/- 0.0011712996342218126</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>0.0013377926421404228 +/- 0.0016932675725436605</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>-4.4408920985006264e-17 +/- 0.00047778308647876687</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.004730052556139464 +/- 0.0011194815588972844</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-0.0005733397037745225 +/- 0.001990699154897246</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>0.00864787386526511 +/- 0.0019519061840244023</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-0.006402293358815136 +/- 0.0010936954746545299</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>4.777830864787225e-05 +/- 0.00014333492594361676</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>-0.006306736741519381 +/- 0.000633850891611178</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>0.0006688963210701893 +/- 0.0014365309487217178</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>0.0004300047778308391 +/- 0.000621118012422364</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>-0.0024844720496895014 +/- 0.0014301604918390764</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>-0.0025800286669852347 +/- 0.0011742193719488138</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-0.003917821309125713 +/- 0.0012784604070959977</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-0.00023889154323941675 +/- 0.00023889154323941675</t>
-        </is>
-      </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-0.001528905876732023 +/- 0.0007937528774885613</t>
+          <t>-0.0006688963210703003 +/- 0.00043789543191170946</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>-0.000286669851887289 +/- 0.00043789543191172405</t>
+          <t>-0.0003344481605351612 +/- 0.00048016605929869044</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-3.3306690738754695e-17 +/- 0.0003700891874063771</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.005494505494505542 +/- 0.001030284694354872</t>
+          <t>-0.0011466794075490228 +/- 0.0011143720773712847</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.0004777830864788335 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-0.00038222646918304457 +/- 0.000633850891611183</t>
+          <t>-0.00023889154323942786 +/- 0.0007166746297181282</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-0.0054945054945055305 +/- 0.0008874426957002428</t>
+          <t>-0.006115623506927892 +/- 0.0012604783524388808</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>-0.004682274247491703 +/- 0.0007339843046219158</t>
+          <t>-0.0007166746297181614 +/- 0.0014687459291867727</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0002866698518873112 +/- 0.0005733397037745113</t>
+          <t>0.0003822264691829669 +/- 0.0005571860386856553</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.004156712852365063 +/- 0.0014019494267674324</t>
+          <t>-0.00286669851887249 +/- 0.001584627229027919</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>-0.006927854753941765 +/- 0.0010078845250706767</t>
+          <t>-0.003965599617773585 +/- 0.0010258437913800295</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>-0.0004777830864787891 +/- 0.0007086668406207244</t>
+          <t>-0.0023411371237458513 +/- 0.0011982738847572377</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>-9.657170449054454e-05 +/- 0.0005200545443877003</t>
+          <t>-0.0034282955094157353 +/- 0.0008208594881699573</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,27 +4891,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.00033800096571708906 +/- 0.0008377282266005482</t>
+          <t>9.657170449057783e-05 +/- 0.0006030901012456247</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0007242877836793782 +/- 0.000755793135803909</t>
+          <t>-0.0012071463061323119 +/- 0.0007242877836793634</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.008836310960888405 +/- 0.000649619702900705</t>
+          <t>-0.008981168517624327 +/- 0.0006183606216738667</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0015451472718493674 +/- 0.0005200545443876715</t>
+          <t>-0.001062288749396434 +/- 0.0006760019314340814</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0005794302269435559 +/- 0.0006405842183206895</t>
+          <t>-0.0002897151134717557 +/- 0.00075424912369933</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4921,62 +4921,62 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-0.014196040560115841 +/- 0.0008137276458885936</t>
+          <t>-0.010864316755190718 +/- 0.0008704855807494037</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.005408015451472692 +/- 0.001198423336165239</t>
+          <t>-0.0005794302269435225 +/- 0.0019168936012823885</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.0062771607918880035 +/- 0.0018701030160344888</t>
+          <t>-0.0014968614196040563 +/- 0.0017064796762020654</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.0010140028971511784 +/- 0.0006277160791887987</t>
+          <t>0.00038628681796235573 +/- 0.0006760019314340908</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.0014002897151135008 +/- 0.0005484218585997207</t>
+          <t>0.00033800096571703355 +/- 0.0003091803108369334</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.00038628681796238907 +/- 0.0005631049632878172</t>
+          <t>-0.0002414292612264557 +/- 0.0006913481923358979</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.004442298406566925 +/- 0.0017649123015448796</t>
+          <t>0.013037180106228886 +/- 0.0018825290863947754</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.007725736359246704 +/- 0.002275078510746445</t>
+          <t>-0.00188314823756639 +/- 0.0014396959455215217</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>9.657170449063335e-05 +/- 0.0006760019314340925</t>
+          <t>-0.009850313858039583 +/- 0.0009705336186500087</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0.002028005794302268 +/- 0.000473102799185558</t>
+          <t>0.0006277160791888115 +/- 0.00043457267020764344</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0024625784645099236 +/- 0.00045552781902736747</t>
+          <t>-0.00019314340898115567 +/- 0.00032029210916032636</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.0002897151134717113 +/- 0.000618360621673858</t>
+          <t>-0.0006277160791888003 +/- 0.000917431192660535</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4986,62 +4986,62 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00024142926122651122 +/- 0.0004947827506499187</t>
+          <t>-0.0028488652824722347 +/- 0.000927540932510777</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.010816030902945407 +/- 0.0014356415980027628</t>
+          <t>-0.007242877836793815 +/- 0.0007480412064138084</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0013520038628682008 +/- 0.0004209463006799018</t>
+          <t>0.0002414292612264446 +/- 0.00024142926122644456</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0008691453404153004 +/- 0.0005200545443876715</t>
+          <t>-0.0006277160791888003 +/- 0.000649619702900715</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.002124577498792868 +/- 0.0006549811668880033</t>
+          <t>-0.0008691453404152782 +/- 0.0006030901012456282</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>9.657170449060005e-05 +/- 0.0001931434089812001</t>
+          <t>-0.001062288749396445 +/- 0.0006030901012456193</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0014968614196040676 +/- 0.00033800096571702244</t>
+          <t>-0.0003380009657170446 +/- 0.0007495980056137046</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.002510864316755146 +/- 0.0012554321583775835</t>
+          <t>-0.00951231289232255 +/- 0.001919931950948436</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0009174311926605117 +/- 0.0009020541618672035</t>
+          <t>-0.0017382906808305009 +/- 0.0008955691449054197</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0006760019314340449 +/- 0.001166880345108124</t>
+          <t>-0.01709319169483341 +/- 0.0024065544750124803</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.657170449062225e-05 +/- 0.0003613382314605682</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.0007242877836794448 +/- 0.00024142926122644456</t>
+          <t>-9.657170449057783e-05 +/- 0.00019314340898115567</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.007484307098020249 +/- 0.0012637616927380318</t>
+          <t>-0.005890873973925648 +/- 0.0011984233361652249</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.008112023177209026 +/- 0.0017516520663657155</t>
+          <t>-0.0002897151134717335 +/- 0.000921235346612215</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>0.0002414292612265001 +/- 0.00024142926122650013</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>0.0004828585224529669 +/- 0.000374020603206915</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.0018348623853211231 +/- 0.0006030901012456211</t>
+          <t>-0.0011588604538870118 +/- 0.0008137276458885841</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>-0.0056977305649444365 +/- 0.002135523359487763</t>
+          <t>-0.011540318686624806 +/- 0.0025038903259225766</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.828585224525561e-05 +/- 0.00040109241250209734</t>
+          <t>-0.0011105746016417228 +/- 0.0005733627275247744</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0008208594881700115 +/- 0.0003771245618496685</t>
+          <t>0.0014485755673587565 +/- 0.00083633549375608</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.0006760019314341337 +/- 0.0005376884947204192</t>
+          <t>-0.007774022211492015 +/- 0.0015185113658634918</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.0013037180106229118 +/- 0.0006845701052031721</t>
+          <t>-0.0003862868179623447 +/- 0.0007725736359246685</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.00014485755673590006 +/- 0.0007178207990013742</t>
+          <t>-0.0013037180106228897 +/- 0.000966923437687139</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>-0.013326895219700596 +/- 0.00188500447087815</t>
+          <t>0.0033317238049251465 +/- 0.0005894039408852456</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0015451472718493674 +/- 0.0005631049632877923</t>
+          <t>-0.00019314340898116678 +/- 0.00038628681796233356</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0010622887493964672 +/- 0.0004209463006799018</t>
+          <t>-0.00014485755673587786 +/- 0.0004852668093249933</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.000289715113471789 +/- 0.0003202921091603766</t>
+          <t>-0.000917431192660556 +/- 0.000589403940885261</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.001158860453887045 +/- 0.00038628681796231134</t>
+          <t>-0.0011588604538870118 +/- 0.0005794302269435058</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0016417189763399676 +/- 0.0010401090887753872</t>
+          <t>0.000917431192660545 +/- 0.0007919468598192442</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.005842588121680326 +/- 0.001593433124094641</t>
+          <t>-0.003524867213906324 +/- 0.0013320245508579149</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>0.002848865282472268 +/- 0.0008487878238168368</t>
+          <t>-0.0016417189763399342 +/- 0.0006183606216738649</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.00028971511347172243 +/- 0.00032029210916035314</t>
+          <t>-0.0013520038628682008 +/- 0.00019314340898115567</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0002414292612264446 +/- 0.00024142926122644456</t>
+          <t>-0.0005311443746982003 +/- 0.00026002727219386355</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>-0.0015934331240946343 +/- 0.0003771245618496629</t>
+          <t>-0.00019314340898116678 +/- 0.00044254714581899913</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.0028005794302269128 +/- 0.0011588604538870164</t>
+          <t>-0.005021728633510358 +/- 0.0013346475095205206</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.0008208594881699338 +/- 0.0016166749437743027</t>
+          <t>-0.0005311443746982225 +/- 0.0006638207187285148</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,77 +5176,77 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>4.828585224530002e-05 +/- 0.00014485755673590006</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>0.0009657170449058783 +/- 0.00048285852245291135</t>
+          <t>4.828585224530002e-05 +/- 0.00040109241250207864</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>0.0018831482375664343 +/- 0.0010677616797438879</t>
+          <t>-0.0009657170449058449 +/- 0.0006107730874299171</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0003740206032069007</t>
+          <t>-0.0005311443746982225 +/- 0.0005041190974848319</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.001207146306132334 +/- 0.00032391134391593064</t>
+          <t>0.0002897151134717557 +/- 0.0004425471458190137</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.0037180106228874577 +/- 0.0009669234376871518</t>
+          <t>-0.0032351521004345685 +/- 0.0007495980056137338</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.0010140028971511895 +/- 0.0007619378965745543</t>
+          <t>4.828585224531112e-05 +/- 0.0005894039408852538</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>0.0013520038628682008 +/- 0.0003613382314605208</t>
+          <t>-0.00014485755673587786 +/- 0.0005311443746982357</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>4.828585224530002e-05 +/- 0.00014485755673590006</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.0025108643167552126 +/- 0.0006030901012456211</t>
+          <t>0.00043457267020761135 +/- 0.00026002727219384913</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.00019314340898121118 +/- 0.0005794302269435132</t>
+          <t>-0.0014485755673587675 +/- 0.0006478226878318778</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.0006760019314341337 +/- 0.0003862868179623502</t>
+          <t>-0.0006760019314340782 +/- 0.0004425471458190258</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>0.0015451472718493674 +/- 0.0005200545443876715</t>
+          <t>0.0004828585224529114 +/- 0.0010578900193243246</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.00019314340898113347 +/- 0.0004924210056584028</t>
+          <t>-0.0005794302269435004 +/- 0.00042094630067994514</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.0008208594881700115 +/- 0.0005311443746981952</t>
+          <t>0.0002414292612264557 +/- 0.0010185911689874001</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-9.657170449060005e-05 +/- 0.0006405842183206911</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.0006277160791888558 +/- 0.0003091803108369334</t>
+          <t>0.00014485755673586674 +/- 0.00022127357290948986</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5271,52 +5271,52 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.0010140028971511784 +/- 0.00045552781902732866</t>
+          <t>-0.00019314340898118898 +/- 0.0006896599158418968</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>0.00014485755673592226 +/- 0.0005311443746982235</t>
+          <t>0.00043457267020763357 +/- 0.00040109241250209734</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-0.00019314340898117787 +/- 0.0003862868179623557</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0004828585224529558 +/- 0.0004318817918879571</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.003911154031868624 +/- 0.001089378481185745</t>
+          <t>-0.00188314823756639 +/- 0.0005484218585997207</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.00024142926122643348 +/- 0.0006567585953035074</t>
+          <t>0.0008691453404152671 +/- 0.00047310279918556477</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>0.0008691453404153116 +/- 0.0003613382314605208</t>
+          <t>-0.0014002897151134896 +/- 0.00033800096571702244</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0007242877836793448 +/- 0.00044517356143373483</t>
+          <t>0.002414292612264601 +/- 0.0007785859727956278</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>0.00033800096571707795 +/- 0.000749598005613711</t>
+          <t>-1.1102230246251566e-17 +/- 0.00043188179188793235</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0007725736359247337 +/- 0.0002365513995927586</t>
+          <t>0.0005311443746982003 +/- 0.00026002727219386355</t>
         </is>
       </c>
     </row>
